--- a/Testing/TEST_RESULTS.xlsx
+++ b/Testing/TEST_RESULTS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Test Details" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Details" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -503,7 +503,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-02-20T18:46:33.657Z</t>
+          <t>2026-02-23T10:59:51.209Z</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-02-20T18:47:17.737Z</t>
+          <t>2026-02-23T11:01:10.597Z</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>44.08 seconds</t>
+          <t>79.39 seconds</t>
         </is>
       </c>
     </row>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9">
@@ -639,17 +639,17 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -660,17 +660,17 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -762,11 +762,11 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>2026-02-20T18:46:34.011Z</t>
+          <t>2026-02-23T10:59:52.579Z</t>
         </is>
       </c>
       <c r="E4" s="9" t="n">
-        <v>1396</v>
+        <v>4583</v>
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
@@ -793,11 +793,11 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>2026-02-20T18:46:35.407Z</t>
+          <t>2026-02-23T10:59:57.163Z</t>
         </is>
       </c>
       <c r="E5" s="9" t="n">
-        <v>120</v>
+        <v>473</v>
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
@@ -824,11 +824,11 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>2026-02-20T18:46:35.527Z</t>
+          <t>2026-02-23T10:59:57.636Z</t>
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>292</v>
+        <v>483</v>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>2026-02-20T18:46:35.820Z</t>
+          <t>2026-02-23T10:59:58.119Z</t>
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>1490</v>
+        <v>2117</v>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
@@ -886,11 +886,11 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>2026-02-20T18:46:37.310Z</t>
+          <t>2026-02-23T11:00:00.236Z</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
@@ -917,11 +917,11 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>2026-02-20T18:46:37.437Z</t>
+          <t>2026-02-23T11:00:00.374Z</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>1973</v>
+        <v>2409</v>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
@@ -948,11 +948,11 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>2026-02-20T18:46:39.410Z</t>
+          <t>2026-02-23T11:00:02.783Z</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>1756</v>
+        <v>2241</v>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
@@ -979,11 +979,11 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>2026-02-20T18:46:41.166Z</t>
+          <t>2026-02-23T11:00:05.024Z</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>1988</v>
+        <v>1603</v>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
@@ -1010,11 +1010,11 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>2026-02-20T18:46:43.154Z</t>
+          <t>2026-02-23T11:00:06.627Z</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>1418</v>
+        <v>1459</v>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
@@ -1041,11 +1041,11 @@
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>2026-02-20T18:46:44.572Z</t>
+          <t>2026-02-23T11:00:08.086Z</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>2184</v>
+        <v>2363</v>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
@@ -1072,11 +1072,11 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>2026-02-20T18:46:46.756Z</t>
+          <t>2026-02-23T11:00:10.449Z</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
@@ -1103,11 +1103,11 @@
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>2026-02-20T18:46:46.829Z</t>
+          <t>2026-02-23T11:00:10.521Z</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
@@ -1134,11 +1134,11 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>2026-02-20T18:46:47.062Z</t>
+          <t>2026-02-23T11:00:10.742Z</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>1569</v>
+        <v>1610</v>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
@@ -1165,11 +1165,11 @@
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>2026-02-20T18:46:48.632Z</t>
+          <t>2026-02-23T11:00:12.352Z</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
@@ -1196,11 +1196,11 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>2026-02-20T18:46:48.739Z</t>
+          <t>2026-02-23T11:00:12.492Z</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>7595</v>
+        <v>8734</v>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
@@ -1227,11 +1227,11 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>2026-02-20T18:46:56.334Z</t>
+          <t>2026-02-23T11:00:21.227Z</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>2105</v>
+        <v>2333</v>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
@@ -1258,11 +1258,11 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>2026-02-20T18:46:58.439Z</t>
+          <t>2026-02-23T11:00:23.560Z</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
@@ -1289,11 +1289,11 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>2026-02-20T18:46:58.648Z</t>
+          <t>2026-02-23T11:00:23.787Z</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>1471</v>
+        <v>1532</v>
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
@@ -1320,11 +1320,11 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>2026-02-20T18:47:00.119Z</t>
+          <t>2026-02-23T11:00:25.319Z</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
@@ -1351,11 +1351,11 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>2026-02-20T18:47:00.251Z</t>
+          <t>2026-02-23T11:00:25.471Z</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>7724</v>
+        <v>7796</v>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
@@ -1382,11 +1382,11 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>2026-02-20T18:47:07.976Z</t>
+          <t>2026-02-23T11:00:33.267Z</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>2159</v>
+        <v>3134</v>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
@@ -1413,11 +1413,11 @@
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>2026-02-20T18:47:10.135Z</t>
+          <t>2026-02-23T11:00:36.401Z</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>69</v>
+        <v>166</v>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
@@ -1444,11 +1444,11 @@
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>2026-02-20T18:47:10.204Z</t>
+          <t>2026-02-23T11:00:36.570Z</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
@@ -1475,11 +1475,11 @@
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>2026-02-20T18:47:10.213Z</t>
+          <t>2026-02-23T11:00:36.600Z</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>416</v>
+        <v>1843</v>
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
@@ -1487,6 +1487,533 @@
         </is>
       </c>
       <c r="G27" s="9" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>T25</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>Drag &amp; Drop column</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-23T11:00:42.335Z</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>622</v>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>T26</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Hide column</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-23T11:00:42.957Z</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>538</v>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>T27</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>Show column</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-23T11:00:43.495Z</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>525</v>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>T28</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>Reset All Columns</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-23T11:00:44.020Z</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>1384</v>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>T29</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>Sort ascending</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-23T11:00:45.405Z</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>558</v>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>T30</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>Sort descending</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-23T11:00:45.963Z</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>532</v>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>T31</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>Sort different column</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-23T11:00:46.495Z</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>532</v>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>T32</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>Persist country tab after logout</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-23T11:00:47.027Z</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>2755</v>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>T33</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>Persist sort after logout</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-23T11:00:49.782Z</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>3396</v>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>T34</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>Single filter</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-23T11:00:53.178Z</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>437</v>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>T35</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>Multiple filters</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-23T11:00:53.615Z</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>423</v>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G38" s="9" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>T36</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>Remove one filter</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-23T11:00:54.038Z</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>428</v>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G39" s="9" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>T37</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>Clear all filters</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-23T11:00:54.466Z</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>490</v>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G40" s="9" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>T38</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>Mixed modifications</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-23T11:00:57.167Z</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>1980</v>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G41" s="9" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>T39</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>Persist all after reload</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-23T11:00:59.147Z</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="n">
+        <v>4728</v>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G42" s="9" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>T40</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>Complete reset</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-23T11:01:03.875Z</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>1724</v>
+      </c>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>T41</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>Final cleanup</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-23T11:01:05.599Z</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="n">
+        <v>4920</v>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G44" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Testing/TEST_RESULTS.xlsx
+++ b/Testing/TEST_RESULTS.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-02-23T10:59:51.209Z</t>
+          <t>2026-02-25T10:48:39.375Z</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-02-23T11:01:10.597Z</t>
+          <t>2026-02-25T10:50:32.899Z</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>79.39 seconds</t>
+          <t>113.52 seconds</t>
         </is>
       </c>
     </row>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8">
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -762,11 +762,11 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T10:59:52.579Z</t>
+          <t>2026-02-25T10:48:43.083Z</t>
         </is>
       </c>
       <c r="E4" s="9" t="n">
-        <v>4583</v>
+        <v>4397</v>
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
@@ -793,11 +793,11 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T10:59:57.163Z</t>
+          <t>2026-02-25T10:48:47.480Z</t>
         </is>
       </c>
       <c r="E5" s="9" t="n">
-        <v>473</v>
+        <v>1074</v>
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
@@ -824,11 +824,11 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T10:59:57.636Z</t>
+          <t>2026-02-25T10:48:48.554Z</t>
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>483</v>
+        <v>1885</v>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T10:59:58.119Z</t>
+          <t>2026-02-25T10:48:50.440Z</t>
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>2117</v>
+        <v>3212</v>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
@@ -886,11 +886,11 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T11:00:00.236Z</t>
+          <t>2026-02-25T10:48:53.653Z</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>137</v>
+        <v>350</v>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
@@ -917,11 +917,11 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T11:00:00.374Z</t>
+          <t>2026-02-25T10:48:54.003Z</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2409</v>
+        <v>3335</v>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
@@ -948,11 +948,11 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T11:00:02.783Z</t>
+          <t>2026-02-25T10:48:57.338Z</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>2241</v>
+        <v>2982</v>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
@@ -979,11 +979,11 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T11:00:05.024Z</t>
+          <t>2026-02-25T10:49:00.321Z</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>1603</v>
+        <v>3183</v>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
@@ -1010,11 +1010,11 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T11:00:06.627Z</t>
+          <t>2026-02-25T10:49:03.505Z</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>1459</v>
+        <v>1993</v>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
@@ -1041,11 +1041,11 @@
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T11:00:08.086Z</t>
+          <t>2026-02-25T10:49:05.499Z</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>2363</v>
+        <v>3481</v>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
@@ -1072,11 +1072,11 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T11:00:10.449Z</t>
+          <t>2026-02-25T10:49:08.981Z</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
@@ -1103,11 +1103,11 @@
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T11:00:10.521Z</t>
+          <t>2026-02-25T10:49:09.077Z</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>221</v>
+        <v>1809</v>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
@@ -1134,11 +1134,11 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T11:00:10.742Z</t>
+          <t>2026-02-25T10:49:10.886Z</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>1610</v>
+        <v>3185</v>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
@@ -1165,11 +1165,11 @@
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T11:00:12.352Z</t>
+          <t>2026-02-25T10:49:14.071Z</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>139</v>
+        <v>365</v>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
@@ -1196,11 +1196,11 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T11:00:12.492Z</t>
+          <t>2026-02-25T10:49:14.437Z</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>8734</v>
+        <v>10957</v>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
@@ -1227,11 +1227,11 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T11:00:21.227Z</t>
+          <t>2026-02-25T10:49:25.394Z</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>2333</v>
+        <v>3361</v>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
@@ -1258,11 +1258,11 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T11:00:23.560Z</t>
+          <t>2026-02-25T10:49:28.755Z</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>227</v>
+        <v>1692</v>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
@@ -1289,11 +1289,11 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T11:00:23.787Z</t>
+          <t>2026-02-25T10:49:30.447Z</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>1532</v>
+        <v>2807</v>
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
@@ -1320,11 +1320,11 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T11:00:25.319Z</t>
+          <t>2026-02-25T10:49:33.254Z</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>152</v>
+        <v>366</v>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
@@ -1351,11 +1351,11 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T11:00:25.471Z</t>
+          <t>2026-02-25T10:49:33.620Z</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>7796</v>
+        <v>10474</v>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
@@ -1382,11 +1382,11 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T11:00:33.267Z</t>
+          <t>2026-02-25T10:49:44.094Z</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>3134</v>
+        <v>3319</v>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
@@ -1413,11 +1413,11 @@
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T11:00:36.401Z</t>
+          <t>2026-02-25T10:49:47.414Z</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>166</v>
+        <v>83</v>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
@@ -1444,11 +1444,11 @@
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T11:00:36.570Z</t>
+          <t>2026-02-25T10:49:47.497Z</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
@@ -1475,11 +1475,11 @@
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T11:00:36.600Z</t>
+          <t>2026-02-25T10:49:47.506Z</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>1843</v>
+        <v>3424</v>
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
@@ -1506,11 +1506,11 @@
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T11:00:42.335Z</t>
+          <t>2026-02-25T10:49:54.566Z</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>622</v>
+        <v>562</v>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T11:00:42.957Z</t>
+          <t>2026-02-25T10:49:55.129Z</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
@@ -1568,11 +1568,11 @@
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T11:00:43.495Z</t>
+          <t>2026-02-25T10:49:55.667Z</t>
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>525</v>
+        <v>543</v>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
@@ -1599,11 +1599,11 @@
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T11:00:44.020Z</t>
+          <t>2026-02-25T10:49:56.210Z</t>
         </is>
       </c>
       <c r="E31" s="9" t="n">
-        <v>1384</v>
+        <v>1712</v>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
@@ -1630,11 +1630,11 @@
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T11:00:45.405Z</t>
+          <t>2026-02-25T10:49:57.923Z</t>
         </is>
       </c>
       <c r="E32" s="9" t="n">
-        <v>558</v>
+        <v>789</v>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
@@ -1661,11 +1661,11 @@
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T11:00:45.963Z</t>
+          <t>2026-02-25T10:49:58.712Z</t>
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>532</v>
+        <v>784</v>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
@@ -1692,11 +1692,11 @@
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T11:00:46.495Z</t>
+          <t>2026-02-25T10:49:59.496Z</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>532</v>
+        <v>792</v>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
@@ -1723,11 +1723,11 @@
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T11:00:47.027Z</t>
+          <t>2026-02-25T10:50:00.288Z</t>
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>2755</v>
+        <v>2628</v>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
@@ -1754,11 +1754,11 @@
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T11:00:49.782Z</t>
+          <t>2026-02-25T10:50:02.917Z</t>
         </is>
       </c>
       <c r="E36" s="9" t="n">
-        <v>3396</v>
+        <v>3431</v>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
@@ -1785,11 +1785,11 @@
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T11:00:53.178Z</t>
+          <t>2026-02-25T10:50:06.348Z</t>
         </is>
       </c>
       <c r="E37" s="9" t="n">
-        <v>437</v>
+        <v>469</v>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
@@ -1816,11 +1816,11 @@
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T11:00:53.615Z</t>
+          <t>2026-02-25T10:50:06.817Z</t>
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
@@ -1847,11 +1847,11 @@
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T11:00:54.038Z</t>
+          <t>2026-02-25T10:50:07.249Z</t>
         </is>
       </c>
       <c r="E39" s="9" t="n">
-        <v>428</v>
+        <v>444</v>
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
@@ -1878,11 +1878,11 @@
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T11:00:54.466Z</t>
+          <t>2026-02-25T10:50:07.693Z</t>
         </is>
       </c>
       <c r="E40" s="9" t="n">
-        <v>490</v>
+        <v>805</v>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
@@ -1909,11 +1909,11 @@
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T11:00:57.167Z</t>
+          <t>2026-02-25T10:50:08.917Z</t>
         </is>
       </c>
       <c r="E41" s="9" t="n">
-        <v>1980</v>
+        <v>5519</v>
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
@@ -1940,11 +1940,11 @@
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T11:00:59.147Z</t>
+          <t>2026-02-25T10:50:14.437Z</t>
         </is>
       </c>
       <c r="E42" s="9" t="n">
-        <v>4728</v>
+        <v>5469</v>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
@@ -1971,11 +1971,11 @@
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>2026-02-23T11:01:03.875Z</t>
+          <t>2026-02-25T10:50:19.906Z</t>
         </is>
       </c>
       <c r="E43" s="9" t="n">
-        <v>1724</v>
+        <v>2015</v>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
@@ -1987,33 +1987,188 @@
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>T41</t>
+          <t>T42</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
+          <t>Login admin for RFQ tests</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T10:50:21.922Z</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="n">
+        <v>359</v>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G44" s="9" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>T43</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>Double-click bond row opens RFQ window</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T10:50:22.281Z</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>2381</v>
+      </c>
+      <c r="F45" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G45" s="9" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>T44</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>RFQ window displays pricing data</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T10:50:24.663Z</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="n">
+        <v>1362</v>
+      </c>
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G46" s="9" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>T45</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>RFQ window draggable and closable</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T10:50:26.025Z</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="n">
+        <v>4592</v>
+      </c>
+      <c r="F47" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G47" s="9" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>T46</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>Open RFQ from OPEN RFQ button</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T10:50:30.617Z</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="n">
+        <v>1574</v>
+      </c>
+      <c r="F48" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G48" s="9" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>T47</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
           <t>Final cleanup</t>
         </is>
       </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>GUI</t>
-        </is>
-      </c>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>2026-02-23T11:01:05.599Z</t>
-        </is>
-      </c>
-      <c r="E44" s="9" t="n">
-        <v>4920</v>
-      </c>
-      <c r="F44" s="10" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G44" s="9" t="n"/>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T10:50:32.191Z</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="n">
+        <v>188</v>
+      </c>
+      <c r="F49" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G49" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Testing/TEST_RESULTS.xlsx
+++ b/Testing/TEST_RESULTS.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,14 +44,10 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00721C24"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="00155724"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -82,12 +78,6 @@
         <bgColor rgb="002196F3"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -107,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -117,14 +107,12 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -515,7 +503,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-02-25T14:32:45.020Z</t>
+          <t>2026-02-25T15:08:09.920Z</t>
         </is>
       </c>
     </row>
@@ -527,7 +515,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-02-25T14:34:25.779Z</t>
+          <t>2026-02-25T15:10:13.500Z</t>
         </is>
       </c>
     </row>
@@ -539,7 +527,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100.76 seconds</t>
+          <t>123.58 seconds</t>
         </is>
       </c>
     </row>
@@ -554,7 +542,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8">
@@ -564,7 +552,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9">
@@ -574,7 +562,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -585,7 +573,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -630,17 +618,17 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -659,7 +647,7 @@
       <c r="D16" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -675,14 +663,14 @@
         <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -700,7 +688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -720,890 +708,1467 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>Start Time</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>Duration (ms)</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>Fail Reason</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>T01</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Login Admin (GUI)</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:08:14.136Z</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>3748</v>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>T02</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Open Admin Panel</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:08:17.884Z</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>1014</v>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Create Admin user</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:08:18.898Z</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>1833</v>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>T04</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Login nuovo Admin</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:08:20.732Z</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>3024</v>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>T05</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Logout Admin-test</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:08:23.756Z</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>354</v>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Disable Admin-test</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:08:24.110Z</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>2923</v>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>T07</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Login utente disabilitato</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:08:27.033Z</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>2949</v>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>T08</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Riattivazione Admin-test</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:08:29.983Z</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>3055</v>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>T09</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Login post-riattivazione</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:08:33.041Z</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>2978</v>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Delete Admin-test</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:08:36.022Z</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>4703</v>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>T11</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Verify DB clean (API)</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:08:40.726Z</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>323</v>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Create Trader user</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:08:41.050Z</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>2373</v>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>T13</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Login Trader</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:08:43.423Z</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>3931</v>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>T14</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Logout Trader</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:08:47.354Z</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>395</v>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>T15</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Disable/Enable Trader cycle</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:08:47.750Z</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>12084</v>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>T16</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Delete Trader</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:08:59.835Z</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>3746</v>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>T17</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Create Viewer user</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:09:03.581Z</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>1728</v>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>T18</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Login Viewer</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:09:05.309Z</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>2565</v>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>T19</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Logout Viewer</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:09:07.874Z</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>353</v>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>T20</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>Disable/Enable Viewer cycle</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>GUI</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>2026-02-25T14:32:47.530Z</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="n">
-        <v>10348</v>
-      </c>
-      <c r="F4" s="11" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G4" s="10" t="inlineStr">
-        <is>
-          <t>User viewer-test not found in table</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:09:08.228Z</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>10936</v>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>T21</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>Delete Viewer</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>GUI</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>2026-02-25T14:32:57.878Z</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>30013</v>
-      </c>
-      <c r="F5" s="11" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G5" s="10" t="inlineStr">
-        <is>
-          <t>Timeout 30s</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:09:19.164Z</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>3733</v>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>T22</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>Verify DB clean (API)</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>2026-02-25T14:33:27.892Z</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>102</v>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:09:22.898Z</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>128</v>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>T23</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>Verify GUI clean</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>GUI</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>2026-02-25T14:33:27.995Z</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:09:23.027Z</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>T24</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>Create users for Section 2</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>GUI</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>2026-02-25T14:33:28.008Z</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>3451</v>
-      </c>
-      <c r="F8" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:09:23.047Z</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>3548</v>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>T25</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>Drag &amp; Drop column</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>GUI</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>2026-02-25T14:33:34.561Z</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>564</v>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G9" s="10" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:09:31.550Z</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>587</v>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>T26</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>Hide column</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>GUI</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>2026-02-25T14:33:35.125Z</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>537</v>
-      </c>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:09:32.137Z</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>541</v>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>T27</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>Show column</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>GUI</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>2026-02-25T14:33:35.662Z</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>539</v>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:09:32.678Z</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>543</v>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>T28</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>Reset All Columns</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>GUI</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>2026-02-25T14:33:36.201Z</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>1685</v>
-      </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:09:33.222Z</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>1737</v>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>T29</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>Sort ascending</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>GUI</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>2026-02-25T14:33:37.886Z</t>
-        </is>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>810</v>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G13" s="10" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:09:34.959Z</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>888</v>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>T30</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>Sort descending</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>GUI</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>2026-02-25T14:33:38.696Z</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>831</v>
-      </c>
-      <c r="F14" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:09:35.847Z</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>877</v>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>T31</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>Sort different column</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>GUI</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>2026-02-25T14:33:39.527Z</t>
-        </is>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>843</v>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G15" s="10" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:09:36.725Z</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>780</v>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>T32</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>Persist country tab after logout</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>GUI</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>2026-02-25T14:33:40.371Z</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>2866</v>
-      </c>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:09:37.505Z</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>3127</v>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>T33</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>Persist sort after logout</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>GUI</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
-        <is>
-          <t>2026-02-25T14:33:43.238Z</t>
-        </is>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>3436</v>
-      </c>
-      <c r="F17" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G17" s="10" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:09:40.632Z</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>3896</v>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>T34</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t>Single filter</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>GUI</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>2026-02-25T14:33:46.674Z</t>
-        </is>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>450</v>
-      </c>
-      <c r="F18" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G18" s="10" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:09:44.529Z</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>468</v>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>T35</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B38" s="9" t="inlineStr">
         <is>
           <t>Multiple filters</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>GUI</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>2026-02-25T14:33:47.124Z</t>
-        </is>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>448</v>
-      </c>
-      <c r="F19" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G19" s="10" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:09:44.997Z</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>454</v>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G38" s="9" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>T36</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B39" s="9" t="inlineStr">
         <is>
           <t>Remove one filter</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>GUI</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>2026-02-25T14:33:47.572Z</t>
-        </is>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>445</v>
-      </c>
-      <c r="F20" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:09:45.451Z</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>461</v>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G39" s="9" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>T37</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B40" s="9" t="inlineStr">
         <is>
           <t>Clear all filters</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>GUI</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>2026-02-25T14:33:48.017Z</t>
-        </is>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>826</v>
-      </c>
-      <c r="F21" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G21" s="10" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:09:45.912Z</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>939</v>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G40" s="9" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>T38</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B41" s="9" t="inlineStr">
         <is>
           <t>Mixed modifications</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>GUI</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>2026-02-25T14:33:49.191Z</t>
-        </is>
-      </c>
-      <c r="E22" s="10" t="n">
-        <v>5476</v>
-      </c>
-      <c r="F22" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G22" s="10" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:09:47.593Z</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>5438</v>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G41" s="9" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>T39</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B42" s="9" t="inlineStr">
         <is>
           <t>Persist all after reload</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>GUI</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>2026-02-25T14:33:54.667Z</t>
-        </is>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>17776</v>
-      </c>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G23" s="10" t="inlineStr">
-        <is>
-          <t>Persist: grid state unavailable after relogin</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:09:53.032Z</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="n">
+        <v>5971</v>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G42" s="9" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>T40</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B43" s="9" t="inlineStr">
         <is>
           <t>Complete reset</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>GUI</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>2026-02-25T14:34:12.443Z</t>
-        </is>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>1973</v>
-      </c>
-      <c r="F24" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G24" s="10" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:09:59.004Z</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>2192</v>
+      </c>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>T42</t>
         </is>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B44" s="9" t="inlineStr">
         <is>
           <t>Login admin for RFQ tests</t>
         </is>
       </c>
-      <c r="C25" s="10" t="inlineStr">
-        <is>
-          <t>GUI</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="inlineStr">
-        <is>
-          <t>2026-02-25T14:34:14.417Z</t>
-        </is>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>333</v>
-      </c>
-      <c r="F25" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G25" s="10" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:10:01.197Z</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="n">
+        <v>337</v>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G44" s="9" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
         <is>
           <t>T43</t>
         </is>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>Double-click bond row opens RFQ window</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>GUI</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="inlineStr">
-        <is>
-          <t>2026-02-25T14:34:14.750Z</t>
-        </is>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>2370</v>
-      </c>
-      <c r="F26" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G26" s="10" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:10:01.534Z</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>2390</v>
+      </c>
+      <c r="F45" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G45" s="9" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
         <is>
           <t>T44</t>
         </is>
       </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B46" s="9" t="inlineStr">
         <is>
           <t>RFQ window displays pricing data</t>
         </is>
       </c>
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t>GUI</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>2026-02-25T14:34:17.120Z</t>
-        </is>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>1364</v>
-      </c>
-      <c r="F27" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G27" s="10" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:10:03.925Z</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G46" s="9" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
         <is>
           <t>T45</t>
         </is>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B47" s="9" t="inlineStr">
         <is>
           <t>RFQ window draggable and closable</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>GUI</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="inlineStr">
-        <is>
-          <t>2026-02-25T14:34:18.484Z</t>
-        </is>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>4576</v>
-      </c>
-      <c r="F28" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G28" s="10" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:10:05.318Z</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="n">
+        <v>4617</v>
+      </c>
+      <c r="F47" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G47" s="9" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
         <is>
           <t>T46</t>
         </is>
       </c>
-      <c r="B29" s="10" t="inlineStr">
+      <c r="B48" s="9" t="inlineStr">
         <is>
           <t>Open RFQ from OPEN RFQ button</t>
         </is>
       </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>GUI</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>2026-02-25T14:34:23.060Z</t>
-        </is>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>1718</v>
-      </c>
-      <c r="F29" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G29" s="10" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:10:09.935Z</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="n">
+        <v>1764</v>
+      </c>
+      <c r="F48" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G48" s="9" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
         <is>
           <t>T47</t>
         </is>
       </c>
-      <c r="B30" s="10" t="inlineStr">
+      <c r="B49" s="9" t="inlineStr">
         <is>
           <t>Final cleanup</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>GUI</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr">
-        <is>
-          <t>2026-02-25T14:34:24.779Z</t>
-        </is>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>328</v>
-      </c>
-      <c r="F30" s="12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G30" s="10" t="n"/>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>2026-02-25T15:10:11.699Z</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="n">
+        <v>497</v>
+      </c>
+      <c r="F49" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G49" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Testing/TEST_RESULTS.xlsx
+++ b/Testing/TEST_RESULTS.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-02-25T15:08:09.920Z</t>
+          <t>2026-02-25T15:17:06.056Z</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-02-25T15:10:13.500Z</t>
+          <t>2026-02-25T15:19:06.748Z</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>123.58 seconds</t>
+          <t>120.69 seconds</t>
         </is>
       </c>
     </row>
@@ -762,11 +762,11 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:08:14.136Z</t>
+          <t>2026-02-25T15:17:11.003Z</t>
         </is>
       </c>
       <c r="E4" s="9" t="n">
-        <v>3748</v>
+        <v>8476</v>
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
@@ -793,11 +793,11 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:08:17.884Z</t>
+          <t>2026-02-25T15:17:19.480Z</t>
         </is>
       </c>
       <c r="E5" s="9" t="n">
-        <v>1014</v>
+        <v>758</v>
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
@@ -824,11 +824,11 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:08:18.898Z</t>
+          <t>2026-02-25T15:17:20.239Z</t>
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>1833</v>
+        <v>1784</v>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:08:20.732Z</t>
+          <t>2026-02-25T15:17:22.023Z</t>
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>3024</v>
+        <v>2813</v>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
@@ -886,11 +886,11 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:08:23.756Z</t>
+          <t>2026-02-25T15:17:24.837Z</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
@@ -917,11 +917,11 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:08:24.110Z</t>
+          <t>2026-02-25T15:17:25.202Z</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2923</v>
+        <v>2970</v>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
@@ -948,11 +948,11 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:08:27.033Z</t>
+          <t>2026-02-25T15:17:28.172Z</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>2949</v>
+        <v>2913</v>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
@@ -979,11 +979,11 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:08:29.983Z</t>
+          <t>2026-02-25T15:17:31.085Z</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>3055</v>
+        <v>2870</v>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
@@ -1010,11 +1010,11 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:08:33.041Z</t>
+          <t>2026-02-25T15:17:33.955Z</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>2978</v>
+        <v>1903</v>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
@@ -1041,11 +1041,11 @@
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:08:36.022Z</t>
+          <t>2026-02-25T15:17:35.858Z</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>4703</v>
+        <v>3641</v>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
@@ -1072,11 +1072,11 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:08:40.726Z</t>
+          <t>2026-02-25T15:17:39.499Z</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>323</v>
+        <v>167</v>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
@@ -1103,11 +1103,11 @@
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:08:41.050Z</t>
+          <t>2026-02-25T15:17:39.667Z</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>2373</v>
+        <v>1814</v>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
@@ -1134,11 +1134,11 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:08:43.423Z</t>
+          <t>2026-02-25T15:17:41.494Z</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>3931</v>
+        <v>2911</v>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
@@ -1165,11 +1165,11 @@
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:08:47.354Z</t>
+          <t>2026-02-25T15:17:44.405Z</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>395</v>
+        <v>335</v>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
@@ -1196,11 +1196,11 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:08:47.750Z</t>
+          <t>2026-02-25T15:17:44.741Z</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>12084</v>
+        <v>10262</v>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
@@ -1227,11 +1227,11 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:08:59.835Z</t>
+          <t>2026-02-25T15:17:55.004Z</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>3746</v>
+        <v>3126</v>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
@@ -1258,11 +1258,11 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:09:03.581Z</t>
+          <t>2026-02-25T15:17:58.131Z</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>1728</v>
+        <v>1718</v>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
@@ -1289,11 +1289,11 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:09:05.309Z</t>
+          <t>2026-02-25T15:17:59.849Z</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>2565</v>
+        <v>2673</v>
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
@@ -1320,11 +1320,11 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:09:07.874Z</t>
+          <t>2026-02-25T15:18:02.522Z</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
@@ -1351,11 +1351,11 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:09:08.228Z</t>
+          <t>2026-02-25T15:18:02.858Z</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>10936</v>
+        <v>10469</v>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
@@ -1382,11 +1382,11 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:09:19.164Z</t>
+          <t>2026-02-25T15:18:13.327Z</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>3733</v>
+        <v>3117</v>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
@@ -1413,11 +1413,11 @@
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:09:22.898Z</t>
+          <t>2026-02-25T15:18:16.444Z</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>128</v>
+        <v>102</v>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
@@ -1444,11 +1444,11 @@
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:09:23.027Z</t>
+          <t>2026-02-25T15:18:16.546Z</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
@@ -1475,11 +1475,11 @@
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:09:23.047Z</t>
+          <t>2026-02-25T15:18:16.558Z</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>3548</v>
+        <v>3349</v>
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
@@ -1506,11 +1506,11 @@
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:09:31.550Z</t>
+          <t>2026-02-25T15:18:24.803Z</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
@@ -1537,11 +1537,11 @@
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:09:32.137Z</t>
+          <t>2026-02-25T15:18:25.394Z</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
@@ -1568,11 +1568,11 @@
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:09:32.678Z</t>
+          <t>2026-02-25T15:18:25.934Z</t>
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
@@ -1599,11 +1599,11 @@
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:09:33.222Z</t>
+          <t>2026-02-25T15:18:26.474Z</t>
         </is>
       </c>
       <c r="E31" s="9" t="n">
-        <v>1737</v>
+        <v>1686</v>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
@@ -1630,11 +1630,11 @@
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:09:34.959Z</t>
+          <t>2026-02-25T15:18:28.160Z</t>
         </is>
       </c>
       <c r="E32" s="9" t="n">
-        <v>888</v>
+        <v>794</v>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
@@ -1661,11 +1661,11 @@
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:09:35.847Z</t>
+          <t>2026-02-25T15:18:28.954Z</t>
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>877</v>
+        <v>822</v>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
@@ -1692,11 +1692,11 @@
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:09:36.725Z</t>
+          <t>2026-02-25T15:18:29.777Z</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>780</v>
+        <v>765</v>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
@@ -1723,11 +1723,11 @@
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:09:37.505Z</t>
+          <t>2026-02-25T15:18:30.542Z</t>
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>3127</v>
+        <v>2672</v>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
@@ -1754,11 +1754,11 @@
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:09:40.632Z</t>
+          <t>2026-02-25T15:18:33.215Z</t>
         </is>
       </c>
       <c r="E36" s="9" t="n">
-        <v>3896</v>
+        <v>3603</v>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
@@ -1785,11 +1785,11 @@
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:09:44.529Z</t>
+          <t>2026-02-25T15:18:36.822Z</t>
         </is>
       </c>
       <c r="E37" s="9" t="n">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:09:44.997Z</t>
+          <t>2026-02-25T15:18:37.301Z</t>
         </is>
       </c>
       <c r="E38" s="9" t="n">
@@ -1847,11 +1847,11 @@
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:09:45.451Z</t>
+          <t>2026-02-25T15:18:37.755Z</t>
         </is>
       </c>
       <c r="E39" s="9" t="n">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
@@ -1878,11 +1878,11 @@
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:09:45.912Z</t>
+          <t>2026-02-25T15:18:38.197Z</t>
         </is>
       </c>
       <c r="E40" s="9" t="n">
-        <v>939</v>
+        <v>778</v>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
@@ -1909,11 +1909,11 @@
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:09:47.593Z</t>
+          <t>2026-02-25T15:18:39.947Z</t>
         </is>
       </c>
       <c r="E41" s="9" t="n">
-        <v>5438</v>
+        <v>5700</v>
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
@@ -1940,11 +1940,11 @@
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:09:53.032Z</t>
+          <t>2026-02-25T15:18:45.651Z</t>
         </is>
       </c>
       <c r="E42" s="9" t="n">
-        <v>5971</v>
+        <v>6530</v>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
@@ -1971,11 +1971,11 @@
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:09:59.004Z</t>
+          <t>2026-02-25T15:18:52.185Z</t>
         </is>
       </c>
       <c r="E43" s="9" t="n">
-        <v>2192</v>
+        <v>2204</v>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
@@ -2002,11 +2002,11 @@
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:10:01.197Z</t>
+          <t>2026-02-25T15:18:54.389Z</t>
         </is>
       </c>
       <c r="E44" s="9" t="n">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
@@ -2033,11 +2033,11 @@
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:10:01.534Z</t>
+          <t>2026-02-25T15:18:54.739Z</t>
         </is>
       </c>
       <c r="E45" s="9" t="n">
-        <v>2390</v>
+        <v>2399</v>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
@@ -2064,11 +2064,11 @@
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:10:03.925Z</t>
+          <t>2026-02-25T15:18:57.139Z</t>
         </is>
       </c>
       <c r="E46" s="9" t="n">
-        <v>1393</v>
+        <v>1383</v>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
@@ -2095,11 +2095,11 @@
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:10:05.318Z</t>
+          <t>2026-02-25T15:18:58.523Z</t>
         </is>
       </c>
       <c r="E47" s="9" t="n">
-        <v>4617</v>
+        <v>4741</v>
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:10:09.935Z</t>
+          <t>2026-02-25T15:19:03.264Z</t>
         </is>
       </c>
       <c r="E48" s="9" t="n">
-        <v>1764</v>
+        <v>1863</v>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
@@ -2157,11 +2157,11 @@
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:10:11.699Z</t>
+          <t>2026-02-25T15:19:05.127Z</t>
         </is>
       </c>
       <c r="E49" s="9" t="n">
-        <v>497</v>
+        <v>437</v>
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>

--- a/Testing/TEST_RESULTS.xlsx
+++ b/Testing/TEST_RESULTS.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-02-25T15:17:06.056Z</t>
+          <t>2026-02-26T14:37:59.458Z</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-02-25T15:19:06.748Z</t>
+          <t>2026-02-26T14:39:41.680Z</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>120.69 seconds</t>
+          <t>102.22 seconds</t>
         </is>
       </c>
     </row>
@@ -762,11 +762,11 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:17:11.003Z</t>
+          <t>2026-02-26T14:38:01.407Z</t>
         </is>
       </c>
       <c r="E4" s="9" t="n">
-        <v>8476</v>
+        <v>2109</v>
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
@@ -793,11 +793,11 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:17:19.480Z</t>
+          <t>2026-02-26T14:38:03.516Z</t>
         </is>
       </c>
       <c r="E5" s="9" t="n">
-        <v>758</v>
+        <v>704</v>
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
@@ -824,11 +824,11 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:17:20.239Z</t>
+          <t>2026-02-26T14:38:04.220Z</t>
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>1784</v>
+        <v>1679</v>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:17:22.023Z</t>
+          <t>2026-02-26T14:38:05.900Z</t>
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>2813</v>
+        <v>2446</v>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
@@ -886,11 +886,11 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:17:24.837Z</t>
+          <t>2026-02-26T14:38:08.347Z</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>364</v>
+        <v>294</v>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
@@ -917,11 +917,11 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:17:25.202Z</t>
+          <t>2026-02-26T14:38:08.642Z</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2970</v>
+        <v>2675</v>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
@@ -948,11 +948,11 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:17:28.172Z</t>
+          <t>2026-02-26T14:38:11.318Z</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>2913</v>
+        <v>2768</v>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
@@ -979,11 +979,11 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:17:31.085Z</t>
+          <t>2026-02-26T14:38:14.086Z</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>2870</v>
+        <v>2628</v>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
@@ -1010,11 +1010,11 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:17:33.955Z</t>
+          <t>2026-02-26T14:38:16.715Z</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>1903</v>
+        <v>1829</v>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
@@ -1041,11 +1041,11 @@
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:17:35.858Z</t>
+          <t>2026-02-26T14:38:18.545Z</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>3641</v>
+        <v>2903</v>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
@@ -1072,11 +1072,11 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:17:39.499Z</t>
+          <t>2026-02-26T14:38:21.449Z</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>167</v>
+        <v>91</v>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
@@ -1103,11 +1103,11 @@
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:17:39.667Z</t>
+          <t>2026-02-26T14:38:21.541Z</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>1814</v>
+        <v>1697</v>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
@@ -1134,11 +1134,11 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:17:41.494Z</t>
+          <t>2026-02-26T14:38:23.238Z</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>2911</v>
+        <v>2352</v>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
@@ -1165,11 +1165,11 @@
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:17:44.405Z</t>
+          <t>2026-02-26T14:38:25.590Z</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>335</v>
+        <v>311</v>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
@@ -1196,11 +1196,11 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:17:44.741Z</t>
+          <t>2026-02-26T14:38:25.902Z</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>10262</v>
+        <v>10400</v>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
@@ -1227,11 +1227,11 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:17:55.004Z</t>
+          <t>2026-02-26T14:38:36.302Z</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>3126</v>
+        <v>3263</v>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
@@ -1258,11 +1258,11 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:17:58.131Z</t>
+          <t>2026-02-26T14:38:39.566Z</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>1718</v>
+        <v>1742</v>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
@@ -1289,11 +1289,11 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:17:59.849Z</t>
+          <t>2026-02-26T14:38:41.309Z</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>2673</v>
+        <v>2532</v>
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
@@ -1320,11 +1320,11 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:18:02.522Z</t>
+          <t>2026-02-26T14:38:43.842Z</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
@@ -1351,11 +1351,11 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:18:02.858Z</t>
+          <t>2026-02-26T14:38:44.183Z</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>10469</v>
+        <v>10281</v>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
@@ -1382,11 +1382,11 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:18:13.327Z</t>
+          <t>2026-02-26T14:38:54.464Z</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>3117</v>
+        <v>3032</v>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
@@ -1413,11 +1413,11 @@
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:18:16.444Z</t>
+          <t>2026-02-26T14:38:57.496Z</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
@@ -1444,11 +1444,11 @@
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:18:16.546Z</t>
+          <t>2026-02-26T14:38:57.582Z</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
@@ -1475,11 +1475,11 @@
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:18:16.558Z</t>
+          <t>2026-02-26T14:38:57.597Z</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>3349</v>
+        <v>3410</v>
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
@@ -1506,11 +1506,11 @@
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:18:24.803Z</t>
+          <t>2026-02-26T14:39:03.951Z</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>591</v>
+        <v>573</v>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
@@ -1537,11 +1537,11 @@
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:18:25.394Z</t>
+          <t>2026-02-26T14:39:04.525Z</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
@@ -1568,11 +1568,11 @@
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:18:25.934Z</t>
+          <t>2026-02-26T14:39:05.071Z</t>
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
@@ -1599,11 +1599,11 @@
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:18:26.474Z</t>
+          <t>2026-02-26T14:39:05.607Z</t>
         </is>
       </c>
       <c r="E31" s="9" t="n">
-        <v>1686</v>
+        <v>1738</v>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
@@ -1630,11 +1630,11 @@
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:18:28.160Z</t>
+          <t>2026-02-26T14:39:07.348Z</t>
         </is>
       </c>
       <c r="E32" s="9" t="n">
-        <v>794</v>
+        <v>861</v>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
@@ -1661,11 +1661,11 @@
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:18:28.954Z</t>
+          <t>2026-02-26T14:39:08.210Z</t>
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>822</v>
+        <v>800</v>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
@@ -1692,11 +1692,11 @@
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:18:29.777Z</t>
+          <t>2026-02-26T14:39:09.010Z</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>765</v>
+        <v>816</v>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
@@ -1723,11 +1723,11 @@
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:18:30.542Z</t>
+          <t>2026-02-26T14:39:09.826Z</t>
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>2672</v>
+        <v>2643</v>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
@@ -1754,11 +1754,11 @@
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:18:33.215Z</t>
+          <t>2026-02-26T14:39:12.469Z</t>
         </is>
       </c>
       <c r="E36" s="9" t="n">
-        <v>3603</v>
+        <v>3422</v>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
@@ -1785,11 +1785,11 @@
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:18:36.822Z</t>
+          <t>2026-02-26T14:39:15.892Z</t>
         </is>
       </c>
       <c r="E37" s="9" t="n">
-        <v>478</v>
+        <v>451</v>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
@@ -1816,11 +1816,11 @@
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:18:37.301Z</t>
+          <t>2026-02-26T14:39:16.343Z</t>
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
@@ -1847,11 +1847,11 @@
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:18:37.755Z</t>
+          <t>2026-02-26T14:39:16.785Z</t>
         </is>
       </c>
       <c r="E39" s="9" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
@@ -1878,11 +1878,11 @@
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:18:38.197Z</t>
+          <t>2026-02-26T14:39:17.229Z</t>
         </is>
       </c>
       <c r="E40" s="9" t="n">
-        <v>778</v>
+        <v>821</v>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
@@ -1909,11 +1909,11 @@
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:18:39.947Z</t>
+          <t>2026-02-26T14:39:18.501Z</t>
         </is>
       </c>
       <c r="E41" s="9" t="n">
-        <v>5700</v>
+        <v>4788</v>
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
@@ -1940,11 +1940,11 @@
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:18:45.651Z</t>
+          <t>2026-02-26T14:39:23.289Z</t>
         </is>
       </c>
       <c r="E42" s="9" t="n">
-        <v>6530</v>
+        <v>5488</v>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
@@ -1971,11 +1971,11 @@
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:18:52.185Z</t>
+          <t>2026-02-26T14:39:28.777Z</t>
         </is>
       </c>
       <c r="E43" s="9" t="n">
-        <v>2204</v>
+        <v>2012</v>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
@@ -2002,11 +2002,11 @@
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:18:54.389Z</t>
+          <t>2026-02-26T14:39:30.790Z</t>
         </is>
       </c>
       <c r="E44" s="9" t="n">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
@@ -2033,11 +2033,11 @@
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:18:54.739Z</t>
+          <t>2026-02-26T14:39:31.162Z</t>
         </is>
       </c>
       <c r="E45" s="9" t="n">
-        <v>2399</v>
+        <v>2389</v>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
@@ -2064,11 +2064,11 @@
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:18:57.139Z</t>
+          <t>2026-02-26T14:39:33.551Z</t>
         </is>
       </c>
       <c r="E46" s="9" t="n">
-        <v>1383</v>
+        <v>1377</v>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
@@ -2095,11 +2095,11 @@
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:18:58.523Z</t>
+          <t>2026-02-26T14:39:34.928Z</t>
         </is>
       </c>
       <c r="E47" s="9" t="n">
-        <v>4741</v>
+        <v>4691</v>
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:19:03.264Z</t>
+          <t>2026-02-26T14:39:39.619Z</t>
         </is>
       </c>
       <c r="E48" s="9" t="n">
-        <v>1863</v>
+        <v>1521</v>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
@@ -2157,11 +2157,11 @@
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>2026-02-25T15:19:05.127Z</t>
+          <t>2026-02-26T14:39:41.140Z</t>
         </is>
       </c>
       <c r="E49" s="9" t="n">
-        <v>437</v>
+        <v>185</v>
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>

--- a/Testing/TEST_RESULTS.xlsx
+++ b/Testing/TEST_RESULTS.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-02-26T14:37:59.458Z</t>
+          <t>2026-02-26T14:48:13.134Z</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-02-26T14:39:41.680Z</t>
+          <t>2026-02-26T14:49:59.095Z</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>102.22 seconds</t>
+          <t>105.96 seconds</t>
         </is>
       </c>
     </row>
@@ -762,11 +762,11 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:38:01.407Z</t>
+          <t>2026-02-26T14:48:15.645Z</t>
         </is>
       </c>
       <c r="E4" s="9" t="n">
-        <v>2109</v>
+        <v>2949</v>
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
@@ -793,11 +793,11 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:38:03.516Z</t>
+          <t>2026-02-26T14:48:18.595Z</t>
         </is>
       </c>
       <c r="E5" s="9" t="n">
-        <v>704</v>
+        <v>926</v>
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
@@ -824,11 +824,11 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:38:04.220Z</t>
+          <t>2026-02-26T14:48:19.522Z</t>
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>1679</v>
+        <v>1803</v>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:38:05.900Z</t>
+          <t>2026-02-26T14:48:21.325Z</t>
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>2446</v>
+        <v>2936</v>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
@@ -886,11 +886,11 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:38:08.347Z</t>
+          <t>2026-02-26T14:48:24.262Z</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>294</v>
+        <v>350</v>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
@@ -917,11 +917,11 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:38:08.642Z</t>
+          <t>2026-02-26T14:48:24.613Z</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2675</v>
+        <v>2771</v>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
@@ -948,11 +948,11 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:38:11.318Z</t>
+          <t>2026-02-26T14:48:27.385Z</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>2768</v>
+        <v>2838</v>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
@@ -979,11 +979,11 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:38:14.086Z</t>
+          <t>2026-02-26T14:48:30.223Z</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>2628</v>
+        <v>2946</v>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
@@ -1010,11 +1010,11 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:38:16.715Z</t>
+          <t>2026-02-26T14:48:33.170Z</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>1829</v>
+        <v>1972</v>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
@@ -1041,11 +1041,11 @@
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:38:18.545Z</t>
+          <t>2026-02-26T14:48:35.142Z</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>2903</v>
+        <v>3328</v>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
@@ -1072,11 +1072,11 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:38:21.449Z</t>
+          <t>2026-02-26T14:48:38.470Z</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
@@ -1103,11 +1103,11 @@
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:38:21.541Z</t>
+          <t>2026-02-26T14:48:38.584Z</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>1697</v>
+        <v>1732</v>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
@@ -1134,11 +1134,11 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:38:23.238Z</t>
+          <t>2026-02-26T14:48:40.316Z</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>2352</v>
+        <v>2644</v>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
@@ -1165,11 +1165,11 @@
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:38:25.590Z</t>
+          <t>2026-02-26T14:48:42.960Z</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
@@ -1196,11 +1196,11 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:38:25.902Z</t>
+          <t>2026-02-26T14:48:43.292Z</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>10400</v>
+        <v>10262</v>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
@@ -1227,11 +1227,11 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:38:36.302Z</t>
+          <t>2026-02-26T14:48:53.555Z</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>3263</v>
+        <v>3064</v>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
@@ -1258,11 +1258,11 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:38:39.566Z</t>
+          <t>2026-02-26T14:48:56.620Z</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>1742</v>
+        <v>1694</v>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
@@ -1289,11 +1289,11 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:38:41.309Z</t>
+          <t>2026-02-26T14:48:58.315Z</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>2532</v>
+        <v>2548</v>
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
@@ -1320,11 +1320,11 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:38:43.842Z</t>
+          <t>2026-02-26T14:49:00.863Z</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>341</v>
+        <v>313</v>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
@@ -1351,11 +1351,11 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:38:44.183Z</t>
+          <t>2026-02-26T14:49:01.176Z</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>10281</v>
+        <v>10231</v>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
@@ -1382,11 +1382,11 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:38:54.464Z</t>
+          <t>2026-02-26T14:49:11.407Z</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>3032</v>
+        <v>3228</v>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
@@ -1413,11 +1413,11 @@
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:38:57.496Z</t>
+          <t>2026-02-26T14:49:14.635Z</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:38:57.582Z</t>
+          <t>2026-02-26T14:49:14.731Z</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
@@ -1475,11 +1475,11 @@
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:38:57.597Z</t>
+          <t>2026-02-26T14:49:14.746Z</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>3410</v>
+        <v>3407</v>
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
@@ -1506,11 +1506,11 @@
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:39:03.951Z</t>
+          <t>2026-02-26T14:49:21.501Z</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
@@ -1537,11 +1537,11 @@
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:39:04.525Z</t>
+          <t>2026-02-26T14:49:22.071Z</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>546</v>
+        <v>529</v>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
@@ -1568,11 +1568,11 @@
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:39:05.071Z</t>
+          <t>2026-02-26T14:49:22.600Z</t>
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
@@ -1599,11 +1599,11 @@
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:39:05.607Z</t>
+          <t>2026-02-26T14:49:23.129Z</t>
         </is>
       </c>
       <c r="E31" s="9" t="n">
-        <v>1738</v>
+        <v>1705</v>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
@@ -1630,11 +1630,11 @@
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:39:07.348Z</t>
+          <t>2026-02-26T14:49:24.835Z</t>
         </is>
       </c>
       <c r="E32" s="9" t="n">
-        <v>861</v>
+        <v>786</v>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
@@ -1661,11 +1661,11 @@
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:39:08.210Z</t>
+          <t>2026-02-26T14:49:25.622Z</t>
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>800</v>
+        <v>767</v>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
@@ -1692,11 +1692,11 @@
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:39:09.010Z</t>
+          <t>2026-02-26T14:49:26.390Z</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>816</v>
+        <v>749</v>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
@@ -1723,11 +1723,11 @@
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:39:09.826Z</t>
+          <t>2026-02-26T14:49:27.140Z</t>
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>2643</v>
+        <v>2586</v>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
@@ -1754,11 +1754,11 @@
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:39:12.469Z</t>
+          <t>2026-02-26T14:49:29.727Z</t>
         </is>
       </c>
       <c r="E36" s="9" t="n">
-        <v>3422</v>
+        <v>3462</v>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
@@ -1785,11 +1785,11 @@
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:39:15.892Z</t>
+          <t>2026-02-26T14:49:33.189Z</t>
         </is>
       </c>
       <c r="E37" s="9" t="n">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
@@ -1816,11 +1816,11 @@
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:39:16.343Z</t>
+          <t>2026-02-26T14:49:33.642Z</t>
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
@@ -1847,11 +1847,11 @@
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:39:16.785Z</t>
+          <t>2026-02-26T14:49:34.074Z</t>
         </is>
       </c>
       <c r="E39" s="9" t="n">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
@@ -1878,11 +1878,11 @@
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:39:17.229Z</t>
+          <t>2026-02-26T14:49:34.520Z</t>
         </is>
       </c>
       <c r="E40" s="9" t="n">
-        <v>821</v>
+        <v>753</v>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
@@ -1909,11 +1909,11 @@
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:39:18.501Z</t>
+          <t>2026-02-26T14:49:35.950Z</t>
         </is>
       </c>
       <c r="E41" s="9" t="n">
-        <v>4788</v>
+        <v>4571</v>
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
@@ -1940,11 +1940,11 @@
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:39:23.289Z</t>
+          <t>2026-02-26T14:49:40.521Z</t>
         </is>
       </c>
       <c r="E42" s="9" t="n">
-        <v>5488</v>
+        <v>5356</v>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
@@ -1971,11 +1971,11 @@
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:39:28.777Z</t>
+          <t>2026-02-26T14:49:45.878Z</t>
         </is>
       </c>
       <c r="E43" s="9" t="n">
-        <v>2012</v>
+        <v>1978</v>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
@@ -2002,11 +2002,11 @@
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:39:30.790Z</t>
+          <t>2026-02-26T14:49:47.857Z</t>
         </is>
       </c>
       <c r="E44" s="9" t="n">
-        <v>372</v>
+        <v>328</v>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
@@ -2033,11 +2033,11 @@
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:39:31.162Z</t>
+          <t>2026-02-26T14:49:48.185Z</t>
         </is>
       </c>
       <c r="E45" s="9" t="n">
-        <v>2389</v>
+        <v>2381</v>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
@@ -2064,11 +2064,11 @@
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:39:33.551Z</t>
+          <t>2026-02-26T14:49:50.566Z</t>
         </is>
       </c>
       <c r="E46" s="9" t="n">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
@@ -2095,11 +2095,11 @@
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:39:34.928Z</t>
+          <t>2026-02-26T14:49:51.945Z</t>
         </is>
       </c>
       <c r="E47" s="9" t="n">
-        <v>4691</v>
+        <v>4663</v>
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:39:39.619Z</t>
+          <t>2026-02-26T14:49:56.609Z</t>
         </is>
       </c>
       <c r="E48" s="9" t="n">
-        <v>1521</v>
+        <v>1588</v>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
@@ -2157,11 +2157,11 @@
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:39:41.140Z</t>
+          <t>2026-02-26T14:49:58.197Z</t>
         </is>
       </c>
       <c r="E49" s="9" t="n">
-        <v>185</v>
+        <v>228</v>
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>

--- a/Testing/TEST_RESULTS.xlsx
+++ b/Testing/TEST_RESULTS.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-02-26T14:48:13.134Z</t>
+          <t>2026-02-27T11:34:06.091Z</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-02-26T14:49:59.095Z</t>
+          <t>2026-02-27T11:35:53.073Z</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>105.96 seconds</t>
+          <t>106.98 seconds</t>
         </is>
       </c>
     </row>
@@ -762,11 +762,11 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:48:15.645Z</t>
+          <t>2026-02-27T11:34:07.055Z</t>
         </is>
       </c>
       <c r="E4" s="9" t="n">
-        <v>2949</v>
+        <v>2055</v>
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
@@ -793,11 +793,11 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:48:18.595Z</t>
+          <t>2026-02-27T11:34:09.111Z</t>
         </is>
       </c>
       <c r="E5" s="9" t="n">
-        <v>926</v>
+        <v>682</v>
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
@@ -824,11 +824,11 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:48:19.522Z</t>
+          <t>2026-02-27T11:34:09.793Z</t>
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>1803</v>
+        <v>1695</v>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:48:21.325Z</t>
+          <t>2026-02-27T11:34:11.489Z</t>
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>2936</v>
+        <v>2679</v>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
@@ -886,11 +886,11 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:48:24.262Z</t>
+          <t>2026-02-27T11:34:14.169Z</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
@@ -917,11 +917,11 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:48:24.613Z</t>
+          <t>2026-02-27T11:34:14.531Z</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2771</v>
+        <v>3027</v>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
@@ -948,11 +948,11 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:48:27.385Z</t>
+          <t>2026-02-27T11:34:17.559Z</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>2838</v>
+        <v>2904</v>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
@@ -979,11 +979,11 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:48:30.223Z</t>
+          <t>2026-02-27T11:34:20.463Z</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>2946</v>
+        <v>2989</v>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
@@ -1010,11 +1010,11 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:48:33.170Z</t>
+          <t>2026-02-27T11:34:23.452Z</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>1972</v>
+        <v>2090</v>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
@@ -1041,11 +1041,11 @@
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:48:35.142Z</t>
+          <t>2026-02-27T11:34:25.542Z</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>3328</v>
+        <v>3690</v>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
@@ -1072,11 +1072,11 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:48:38.470Z</t>
+          <t>2026-02-27T11:34:29.233Z</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
@@ -1103,11 +1103,11 @@
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:48:38.584Z</t>
+          <t>2026-02-27T11:34:29.315Z</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>1732</v>
+        <v>1758</v>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
@@ -1134,11 +1134,11 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:48:40.316Z</t>
+          <t>2026-02-27T11:34:31.073Z</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>2644</v>
+        <v>2729</v>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
@@ -1165,11 +1165,11 @@
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:48:42.960Z</t>
+          <t>2026-02-27T11:34:33.802Z</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>332</v>
+        <v>360</v>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
@@ -1196,11 +1196,11 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:48:43.292Z</t>
+          <t>2026-02-27T11:34:34.162Z</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>10262</v>
+        <v>10648</v>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
@@ -1227,11 +1227,11 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:48:53.555Z</t>
+          <t>2026-02-27T11:34:44.811Z</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>3064</v>
+        <v>3345</v>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
@@ -1258,11 +1258,11 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:48:56.620Z</t>
+          <t>2026-02-27T11:34:48.156Z</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>1694</v>
+        <v>1714</v>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
@@ -1289,11 +1289,11 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:48:58.315Z</t>
+          <t>2026-02-27T11:34:49.870Z</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>2548</v>
+        <v>2707</v>
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
@@ -1320,11 +1320,11 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:49:00.863Z</t>
+          <t>2026-02-27T11:34:52.577Z</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>313</v>
+        <v>351</v>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
@@ -1351,11 +1351,11 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:49:01.176Z</t>
+          <t>2026-02-27T11:34:52.929Z</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>10231</v>
+        <v>10764</v>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
@@ -1382,11 +1382,11 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:49:11.407Z</t>
+          <t>2026-02-27T11:35:03.693Z</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>3228</v>
+        <v>3472</v>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
@@ -1413,11 +1413,11 @@
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:49:14.635Z</t>
+          <t>2026-02-27T11:35:07.166Z</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
@@ -1444,11 +1444,11 @@
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:49:14.731Z</t>
+          <t>2026-02-27T11:35:07.249Z</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
@@ -1475,11 +1475,11 @@
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:49:14.746Z</t>
+          <t>2026-02-27T11:35:07.267Z</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>3407</v>
+        <v>3539</v>
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
@@ -1506,11 +1506,11 @@
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:49:21.501Z</t>
+          <t>2026-02-27T11:35:13.553Z</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>570</v>
+        <v>589</v>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
@@ -1537,11 +1537,11 @@
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:49:22.071Z</t>
+          <t>2026-02-27T11:35:14.142Z</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>529</v>
+        <v>552</v>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
@@ -1568,11 +1568,11 @@
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:49:22.600Z</t>
+          <t>2026-02-27T11:35:14.694Z</t>
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
@@ -1599,11 +1599,11 @@
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:49:23.129Z</t>
+          <t>2026-02-27T11:35:15.230Z</t>
         </is>
       </c>
       <c r="E31" s="9" t="n">
-        <v>1705</v>
+        <v>1688</v>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
@@ -1630,11 +1630,11 @@
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:49:24.835Z</t>
+          <t>2026-02-27T11:35:16.919Z</t>
         </is>
       </c>
       <c r="E32" s="9" t="n">
-        <v>786</v>
+        <v>842</v>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
@@ -1661,11 +1661,11 @@
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:49:25.622Z</t>
+          <t>2026-02-27T11:35:17.762Z</t>
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>767</v>
+        <v>846</v>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
@@ -1692,11 +1692,11 @@
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:49:26.390Z</t>
+          <t>2026-02-27T11:35:18.608Z</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>749</v>
+        <v>835</v>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
@@ -1723,11 +1723,11 @@
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:49:27.140Z</t>
+          <t>2026-02-27T11:35:19.443Z</t>
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>2586</v>
+        <v>5646</v>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
@@ -1754,11 +1754,11 @@
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:49:29.727Z</t>
+          <t>2026-02-27T11:35:25.089Z</t>
         </is>
       </c>
       <c r="E36" s="9" t="n">
-        <v>3462</v>
+        <v>2927</v>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
@@ -1785,11 +1785,11 @@
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:49:33.189Z</t>
+          <t>2026-02-27T11:35:28.017Z</t>
         </is>
       </c>
       <c r="E37" s="9" t="n">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
@@ -1816,11 +1816,11 @@
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:49:33.642Z</t>
+          <t>2026-02-27T11:35:28.473Z</t>
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>431</v>
+        <v>447</v>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
@@ -1847,11 +1847,11 @@
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:49:34.074Z</t>
+          <t>2026-02-27T11:35:28.921Z</t>
         </is>
       </c>
       <c r="E39" s="9" t="n">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
@@ -1878,11 +1878,11 @@
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:49:34.520Z</t>
+          <t>2026-02-27T11:35:29.373Z</t>
         </is>
       </c>
       <c r="E40" s="9" t="n">
-        <v>753</v>
+        <v>845</v>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
@@ -1909,11 +1909,11 @@
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:49:35.950Z</t>
+          <t>2026-02-27T11:35:30.220Z</t>
         </is>
       </c>
       <c r="E41" s="9" t="n">
-        <v>4571</v>
+        <v>4392</v>
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
@@ -1940,11 +1940,11 @@
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:49:40.521Z</t>
+          <t>2026-02-27T11:35:34.612Z</t>
         </is>
       </c>
       <c r="E42" s="9" t="n">
-        <v>5356</v>
+        <v>5376</v>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
@@ -1971,11 +1971,11 @@
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:49:45.878Z</t>
+          <t>2026-02-27T11:35:39.988Z</t>
         </is>
       </c>
       <c r="E43" s="9" t="n">
-        <v>1978</v>
+        <v>2040</v>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
@@ -2002,11 +2002,11 @@
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:49:47.857Z</t>
+          <t>2026-02-27T11:35:42.029Z</t>
         </is>
       </c>
       <c r="E44" s="9" t="n">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
@@ -2033,11 +2033,11 @@
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:49:48.185Z</t>
+          <t>2026-02-27T11:35:42.362Z</t>
         </is>
       </c>
       <c r="E45" s="9" t="n">
-        <v>2381</v>
+        <v>2471</v>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
@@ -2064,11 +2064,11 @@
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:49:50.566Z</t>
+          <t>2026-02-27T11:35:44.834Z</t>
         </is>
       </c>
       <c r="E46" s="9" t="n">
-        <v>1379</v>
+        <v>1366</v>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
@@ -2095,11 +2095,11 @@
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:49:51.945Z</t>
+          <t>2026-02-27T11:35:46.200Z</t>
         </is>
       </c>
       <c r="E47" s="9" t="n">
-        <v>4663</v>
+        <v>4726</v>
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:49:56.609Z</t>
+          <t>2026-02-27T11:35:50.926Z</t>
         </is>
       </c>
       <c r="E48" s="9" t="n">
-        <v>1588</v>
+        <v>1582</v>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
@@ -2157,11 +2157,11 @@
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>2026-02-26T14:49:58.197Z</t>
+          <t>2026-02-27T11:35:52.509Z</t>
         </is>
       </c>
       <c r="E49" s="9" t="n">
-        <v>228</v>
+        <v>178</v>
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>

--- a/Testing/TEST_RESULTS.xlsx
+++ b/Testing/TEST_RESULTS.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-02-27T11:34:06.091Z</t>
+          <t>2026-02-27T14:14:13.792Z</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-02-27T11:35:53.073Z</t>
+          <t>2026-02-27T14:15:53.547Z</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>106.98 seconds</t>
+          <t>99.75 seconds</t>
         </is>
       </c>
     </row>
@@ -762,11 +762,11 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:34:07.055Z</t>
+          <t>2026-02-27T14:14:16.377Z</t>
         </is>
       </c>
       <c r="E4" s="9" t="n">
-        <v>2055</v>
+        <v>2595</v>
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
@@ -793,11 +793,11 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:34:09.111Z</t>
+          <t>2026-02-27T14:14:18.972Z</t>
         </is>
       </c>
       <c r="E5" s="9" t="n">
-        <v>682</v>
+        <v>712</v>
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
@@ -824,11 +824,11 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:34:09.793Z</t>
+          <t>2026-02-27T14:14:19.684Z</t>
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>1695</v>
+        <v>1732</v>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:34:11.489Z</t>
+          <t>2026-02-27T14:14:21.416Z</t>
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>2679</v>
+        <v>2468</v>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
@@ -886,11 +886,11 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:34:14.169Z</t>
+          <t>2026-02-27T14:14:23.884Z</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>362</v>
+        <v>312</v>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
@@ -917,11 +917,11 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:34:14.531Z</t>
+          <t>2026-02-27T14:14:24.197Z</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>3027</v>
+        <v>2602</v>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
@@ -948,11 +948,11 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:34:17.559Z</t>
+          <t>2026-02-27T14:14:26.799Z</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>2904</v>
+        <v>2772</v>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
@@ -979,11 +979,11 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:34:20.463Z</t>
+          <t>2026-02-27T14:14:29.571Z</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>2989</v>
+        <v>2591</v>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
@@ -1010,11 +1010,11 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:34:23.452Z</t>
+          <t>2026-02-27T14:14:32.162Z</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>2090</v>
+        <v>1765</v>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
@@ -1041,11 +1041,11 @@
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:34:25.542Z</t>
+          <t>2026-02-27T14:14:33.928Z</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>3690</v>
+        <v>2882</v>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
@@ -1072,11 +1072,11 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:34:29.233Z</t>
+          <t>2026-02-27T14:14:36.810Z</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
@@ -1103,11 +1103,11 @@
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:34:29.315Z</t>
+          <t>2026-02-27T14:14:36.898Z</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>1758</v>
+        <v>1668</v>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
@@ -1134,11 +1134,11 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:34:31.073Z</t>
+          <t>2026-02-27T14:14:38.566Z</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>2729</v>
+        <v>2353</v>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
@@ -1165,11 +1165,11 @@
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:34:33.802Z</t>
+          <t>2026-02-27T14:14:40.920Z</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>360</v>
+        <v>295</v>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
@@ -1196,11 +1196,11 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:34:34.162Z</t>
+          <t>2026-02-27T14:14:41.215Z</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>10648</v>
+        <v>9646</v>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
@@ -1227,11 +1227,11 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:34:44.811Z</t>
+          <t>2026-02-27T14:14:50.861Z</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>3345</v>
+        <v>2869</v>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
@@ -1258,11 +1258,11 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:34:48.156Z</t>
+          <t>2026-02-27T14:14:53.731Z</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>1714</v>
+        <v>1670</v>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
@@ -1289,11 +1289,11 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:34:49.870Z</t>
+          <t>2026-02-27T14:14:55.402Z</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>2707</v>
+        <v>2396</v>
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
@@ -1320,11 +1320,11 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:34:52.577Z</t>
+          <t>2026-02-27T14:14:57.799Z</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>351</v>
+        <v>296</v>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
@@ -1351,11 +1351,11 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:34:52.929Z</t>
+          <t>2026-02-27T14:14:58.096Z</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>10764</v>
+        <v>9685</v>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
@@ -1382,11 +1382,11 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:35:03.693Z</t>
+          <t>2026-02-27T14:15:07.782Z</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>3472</v>
+        <v>2867</v>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
@@ -1413,11 +1413,11 @@
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:35:07.166Z</t>
+          <t>2026-02-27T14:15:10.650Z</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
@@ -1444,11 +1444,11 @@
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:35:07.249Z</t>
+          <t>2026-02-27T14:15:10.734Z</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
@@ -1475,11 +1475,11 @@
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:35:07.267Z</t>
+          <t>2026-02-27T14:15:10.748Z</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>3539</v>
+        <v>3344</v>
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
@@ -1506,11 +1506,11 @@
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:35:13.553Z</t>
+          <t>2026-02-27T14:15:16.353Z</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>589</v>
+        <v>544</v>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
@@ -1537,11 +1537,11 @@
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:35:14.142Z</t>
+          <t>2026-02-27T14:15:16.897Z</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>552</v>
+        <v>539</v>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
@@ -1568,11 +1568,11 @@
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:35:14.694Z</t>
+          <t>2026-02-27T14:15:17.437Z</t>
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
@@ -1599,11 +1599,11 @@
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:35:15.230Z</t>
+          <t>2026-02-27T14:15:17.973Z</t>
         </is>
       </c>
       <c r="E31" s="9" t="n">
-        <v>1688</v>
+        <v>1604</v>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
@@ -1630,11 +1630,11 @@
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:35:16.919Z</t>
+          <t>2026-02-27T14:15:19.578Z</t>
         </is>
       </c>
       <c r="E32" s="9" t="n">
-        <v>842</v>
+        <v>773</v>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
@@ -1661,11 +1661,11 @@
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:35:17.762Z</t>
+          <t>2026-02-27T14:15:20.352Z</t>
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>846</v>
+        <v>784</v>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
@@ -1692,11 +1692,11 @@
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:35:18.608Z</t>
+          <t>2026-02-27T14:15:21.136Z</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>835</v>
+        <v>751</v>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
@@ -1723,11 +1723,11 @@
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:35:19.443Z</t>
+          <t>2026-02-27T14:15:21.887Z</t>
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>5646</v>
+        <v>5203</v>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
@@ -1754,11 +1754,11 @@
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:35:25.089Z</t>
+          <t>2026-02-27T14:15:27.091Z</t>
         </is>
       </c>
       <c r="E36" s="9" t="n">
-        <v>2927</v>
+        <v>2662</v>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
@@ -1785,11 +1785,11 @@
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:35:28.017Z</t>
+          <t>2026-02-27T14:15:29.753Z</t>
         </is>
       </c>
       <c r="E37" s="9" t="n">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
@@ -1816,11 +1816,11 @@
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:35:28.473Z</t>
+          <t>2026-02-27T14:15:30.189Z</t>
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
@@ -1847,11 +1847,11 @@
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:35:28.921Z</t>
+          <t>2026-02-27T14:15:30.622Z</t>
         </is>
       </c>
       <c r="E39" s="9" t="n">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
@@ -1878,11 +1878,11 @@
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:35:29.373Z</t>
+          <t>2026-02-27T14:15:31.066Z</t>
         </is>
       </c>
       <c r="E40" s="9" t="n">
-        <v>845</v>
+        <v>787</v>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
@@ -1909,11 +1909,11 @@
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:35:30.220Z</t>
+          <t>2026-02-27T14:15:31.855Z</t>
         </is>
       </c>
       <c r="E41" s="9" t="n">
-        <v>4392</v>
+        <v>4000</v>
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
@@ -1940,11 +1940,11 @@
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:35:34.612Z</t>
+          <t>2026-02-27T14:15:35.855Z</t>
         </is>
       </c>
       <c r="E42" s="9" t="n">
-        <v>5376</v>
+        <v>5170</v>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
@@ -1971,11 +1971,11 @@
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:35:39.988Z</t>
+          <t>2026-02-27T14:15:41.026Z</t>
         </is>
       </c>
       <c r="E43" s="9" t="n">
-        <v>2040</v>
+        <v>1895</v>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
@@ -2002,11 +2002,11 @@
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:35:42.029Z</t>
+          <t>2026-02-27T14:15:42.921Z</t>
         </is>
       </c>
       <c r="E44" s="9" t="n">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
@@ -2033,11 +2033,11 @@
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:35:42.362Z</t>
+          <t>2026-02-27T14:15:43.250Z</t>
         </is>
       </c>
       <c r="E45" s="9" t="n">
-        <v>2471</v>
+        <v>2380</v>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:35:44.834Z</t>
+          <t>2026-02-27T14:15:45.629Z</t>
         </is>
       </c>
       <c r="E46" s="9" t="n">
@@ -2095,11 +2095,11 @@
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:35:46.200Z</t>
+          <t>2026-02-27T14:15:46.995Z</t>
         </is>
       </c>
       <c r="E47" s="9" t="n">
-        <v>4726</v>
+        <v>4526</v>
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:35:50.926Z</t>
+          <t>2026-02-27T14:15:51.521Z</t>
         </is>
       </c>
       <c r="E48" s="9" t="n">
-        <v>1582</v>
+        <v>1523</v>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
@@ -2157,11 +2157,11 @@
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T11:35:52.509Z</t>
+          <t>2026-02-27T14:15:53.044Z</t>
         </is>
       </c>
       <c r="E49" s="9" t="n">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>

--- a/Testing/TEST_RESULTS.xlsx
+++ b/Testing/TEST_RESULTS.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-02-27T14:14:13.792Z</t>
+          <t>2026-02-27T16:08:42.265Z</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-02-27T14:15:53.547Z</t>
+          <t>2026-02-27T16:10:26.751Z</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>99.75 seconds</t>
+          <t>104.49 seconds</t>
         </is>
       </c>
     </row>
@@ -762,11 +762,11 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:14:16.377Z</t>
+          <t>2026-02-27T16:08:47.765Z</t>
         </is>
       </c>
       <c r="E4" s="9" t="n">
-        <v>2595</v>
+        <v>2107</v>
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
@@ -793,11 +793,11 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:14:18.972Z</t>
+          <t>2026-02-27T16:08:49.872Z</t>
         </is>
       </c>
       <c r="E5" s="9" t="n">
-        <v>712</v>
+        <v>881</v>
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
@@ -824,11 +824,11 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:14:19.684Z</t>
+          <t>2026-02-27T16:08:50.753Z</t>
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>1732</v>
+        <v>1753</v>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:14:21.416Z</t>
+          <t>2026-02-27T16:08:52.507Z</t>
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>2468</v>
+        <v>2463</v>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
@@ -886,11 +886,11 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:14:23.884Z</t>
+          <t>2026-02-27T16:08:54.970Z</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
@@ -917,11 +917,11 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:14:24.197Z</t>
+          <t>2026-02-27T16:08:55.274Z</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2602</v>
+        <v>2929</v>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
@@ -948,11 +948,11 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:14:26.799Z</t>
+          <t>2026-02-27T16:08:58.203Z</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>2772</v>
+        <v>2755</v>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
@@ -979,11 +979,11 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:14:29.571Z</t>
+          <t>2026-02-27T16:09:00.959Z</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>2591</v>
+        <v>2675</v>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
@@ -1010,11 +1010,11 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:14:32.162Z</t>
+          <t>2026-02-27T16:09:03.635Z</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>1765</v>
+        <v>1809</v>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
@@ -1041,11 +1041,11 @@
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:14:33.928Z</t>
+          <t>2026-02-27T16:09:05.445Z</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>2882</v>
+        <v>3117</v>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
@@ -1072,11 +1072,11 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:14:36.810Z</t>
+          <t>2026-02-27T16:09:08.562Z</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
@@ -1103,11 +1103,11 @@
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:14:36.898Z</t>
+          <t>2026-02-27T16:09:08.654Z</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>1668</v>
+        <v>1675</v>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
@@ -1134,11 +1134,11 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:14:38.566Z</t>
+          <t>2026-02-27T16:09:10.329Z</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>2353</v>
+        <v>2373</v>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
@@ -1165,11 +1165,11 @@
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:14:40.920Z</t>
+          <t>2026-02-27T16:09:12.703Z</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
@@ -1196,11 +1196,11 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:14:41.215Z</t>
+          <t>2026-02-27T16:09:13.000Z</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>9646</v>
+        <v>9890</v>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
@@ -1227,11 +1227,11 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:14:50.861Z</t>
+          <t>2026-02-27T16:09:22.890Z</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>2869</v>
+        <v>2972</v>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
@@ -1258,11 +1258,11 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:14:53.731Z</t>
+          <t>2026-02-27T16:09:25.863Z</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>1670</v>
+        <v>1710</v>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
@@ -1289,11 +1289,11 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:14:55.402Z</t>
+          <t>2026-02-27T16:09:27.573Z</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>2396</v>
+        <v>2346</v>
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
@@ -1320,11 +1320,11 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:14:57.799Z</t>
+          <t>2026-02-27T16:09:29.919Z</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
@@ -1351,11 +1351,11 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:14:58.096Z</t>
+          <t>2026-02-27T16:09:30.212Z</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>9685</v>
+        <v>9891</v>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
@@ -1382,11 +1382,11 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:15:07.782Z</t>
+          <t>2026-02-27T16:09:40.103Z</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>2867</v>
+        <v>2992</v>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
@@ -1413,11 +1413,11 @@
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:15:10.650Z</t>
+          <t>2026-02-27T16:09:43.095Z</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:15:10.734Z</t>
+          <t>2026-02-27T16:09:43.180Z</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
@@ -1475,11 +1475,11 @@
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:15:10.748Z</t>
+          <t>2026-02-27T16:09:43.193Z</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>3344</v>
+        <v>3347</v>
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
@@ -1506,11 +1506,11 @@
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:15:16.353Z</t>
+          <t>2026-02-27T16:09:48.860Z</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>544</v>
+        <v>555</v>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
@@ -1537,11 +1537,11 @@
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:15:16.897Z</t>
+          <t>2026-02-27T16:09:49.415Z</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
@@ -1568,11 +1568,11 @@
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:15:17.437Z</t>
+          <t>2026-02-27T16:09:49.950Z</t>
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:15:17.973Z</t>
+          <t>2026-02-27T16:09:50.484Z</t>
         </is>
       </c>
       <c r="E31" s="9" t="n">
@@ -1630,11 +1630,11 @@
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:15:19.578Z</t>
+          <t>2026-02-27T16:09:52.088Z</t>
         </is>
       </c>
       <c r="E32" s="9" t="n">
-        <v>773</v>
+        <v>863</v>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
@@ -1661,11 +1661,11 @@
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:15:20.352Z</t>
+          <t>2026-02-27T16:09:52.952Z</t>
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>784</v>
+        <v>816</v>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
@@ -1692,11 +1692,11 @@
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:15:21.136Z</t>
+          <t>2026-02-27T16:09:53.768Z</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>751</v>
+        <v>799</v>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
@@ -1723,11 +1723,11 @@
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:15:21.887Z</t>
+          <t>2026-02-27T16:09:54.567Z</t>
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>5203</v>
+        <v>5372</v>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
@@ -1754,11 +1754,11 @@
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:15:27.091Z</t>
+          <t>2026-02-27T16:09:59.939Z</t>
         </is>
       </c>
       <c r="E36" s="9" t="n">
-        <v>2662</v>
+        <v>2656</v>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
@@ -1785,11 +1785,11 @@
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:15:29.753Z</t>
+          <t>2026-02-27T16:10:02.596Z</t>
         </is>
       </c>
       <c r="E37" s="9" t="n">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
@@ -1816,11 +1816,11 @@
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:15:30.189Z</t>
+          <t>2026-02-27T16:10:03.038Z</t>
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
@@ -1847,11 +1847,11 @@
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:15:30.622Z</t>
+          <t>2026-02-27T16:10:03.469Z</t>
         </is>
       </c>
       <c r="E39" s="9" t="n">
-        <v>443</v>
+        <v>457</v>
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
@@ -1878,11 +1878,11 @@
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:15:31.066Z</t>
+          <t>2026-02-27T16:10:03.927Z</t>
         </is>
       </c>
       <c r="E40" s="9" t="n">
-        <v>787</v>
+        <v>765</v>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
@@ -1909,11 +1909,11 @@
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:15:31.855Z</t>
+          <t>2026-02-27T16:10:04.695Z</t>
         </is>
       </c>
       <c r="E41" s="9" t="n">
-        <v>4000</v>
+        <v>4161</v>
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
@@ -1940,11 +1940,11 @@
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:15:35.855Z</t>
+          <t>2026-02-27T16:10:08.856Z</t>
         </is>
       </c>
       <c r="E42" s="9" t="n">
-        <v>5170</v>
+        <v>5216</v>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
@@ -1971,11 +1971,11 @@
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:15:41.026Z</t>
+          <t>2026-02-27T16:10:14.072Z</t>
         </is>
       </c>
       <c r="E43" s="9" t="n">
-        <v>1895</v>
+        <v>1998</v>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
@@ -2002,11 +2002,11 @@
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:15:42.921Z</t>
+          <t>2026-02-27T16:10:16.071Z</t>
         </is>
       </c>
       <c r="E44" s="9" t="n">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
@@ -2033,11 +2033,11 @@
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:15:43.250Z</t>
+          <t>2026-02-27T16:10:16.409Z</t>
         </is>
       </c>
       <c r="E45" s="9" t="n">
-        <v>2380</v>
+        <v>2367</v>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
@@ -2064,11 +2064,11 @@
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:15:45.629Z</t>
+          <t>2026-02-27T16:10:18.777Z</t>
         </is>
       </c>
       <c r="E46" s="9" t="n">
-        <v>1366</v>
+        <v>1369</v>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
@@ -2095,11 +2095,11 @@
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:15:46.995Z</t>
+          <t>2026-02-27T16:10:20.146Z</t>
         </is>
       </c>
       <c r="E47" s="9" t="n">
-        <v>4526</v>
+        <v>4501</v>
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:15:51.521Z</t>
+          <t>2026-02-27T16:10:24.647Z</t>
         </is>
       </c>
       <c r="E48" s="9" t="n">
-        <v>1523</v>
+        <v>1576</v>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
@@ -2157,11 +2157,11 @@
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T14:15:53.044Z</t>
+          <t>2026-02-27T16:10:26.223Z</t>
         </is>
       </c>
       <c r="E49" s="9" t="n">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>

--- a/Testing/TEST_RESULTS.xlsx
+++ b/Testing/TEST_RESULTS.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-02-27T16:08:42.265Z</t>
+          <t>2026-02-27T18:08:58.103Z</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-02-27T16:10:26.751Z</t>
+          <t>2026-02-27T18:11:01.267Z</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>104.49 seconds</t>
+          <t>123.16 seconds</t>
         </is>
       </c>
     </row>
@@ -762,11 +762,11 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:08:47.765Z</t>
+          <t>2026-02-27T18:08:59.900Z</t>
         </is>
       </c>
       <c r="E4" s="9" t="n">
-        <v>2107</v>
+        <v>3699</v>
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
@@ -793,11 +793,11 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:08:49.872Z</t>
+          <t>2026-02-27T18:09:03.599Z</t>
         </is>
       </c>
       <c r="E5" s="9" t="n">
-        <v>881</v>
+        <v>812</v>
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
@@ -824,11 +824,11 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:08:50.753Z</t>
+          <t>2026-02-27T18:09:04.412Z</t>
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>1753</v>
+        <v>1707</v>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:08:52.507Z</t>
+          <t>2026-02-27T18:09:06.121Z</t>
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>2463</v>
+        <v>3363</v>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
@@ -886,11 +886,11 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:08:54.970Z</t>
+          <t>2026-02-27T18:09:09.485Z</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>304</v>
+        <v>325</v>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
@@ -917,11 +917,11 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:08:55.274Z</t>
+          <t>2026-02-27T18:09:09.810Z</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2929</v>
+        <v>3336</v>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
@@ -948,11 +948,11 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:08:58.203Z</t>
+          <t>2026-02-27T18:09:13.147Z</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>2755</v>
+        <v>2777</v>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
@@ -979,11 +979,11 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:09:00.959Z</t>
+          <t>2026-02-27T18:09:15.924Z</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>2675</v>
+        <v>3373</v>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
@@ -1010,11 +1010,11 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:09:03.635Z</t>
+          <t>2026-02-27T18:09:19.297Z</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>1809</v>
+        <v>2515</v>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
@@ -1041,11 +1041,11 @@
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:09:05.445Z</t>
+          <t>2026-02-27T18:09:21.812Z</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>3117</v>
+        <v>3681</v>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
@@ -1072,11 +1072,11 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:09:08.562Z</t>
+          <t>2026-02-27T18:09:25.494Z</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>91</v>
+        <v>667</v>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
@@ -1103,11 +1103,11 @@
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:09:08.654Z</t>
+          <t>2026-02-27T18:09:26.162Z</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>1675</v>
+        <v>4240</v>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
@@ -1134,11 +1134,11 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:09:10.329Z</t>
+          <t>2026-02-27T18:09:30.402Z</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>2373</v>
+        <v>3232</v>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
@@ -1165,11 +1165,11 @@
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:09:12.703Z</t>
+          <t>2026-02-27T18:09:33.634Z</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
@@ -1196,11 +1196,11 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:09:13.000Z</t>
+          <t>2026-02-27T18:09:33.941Z</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>9890</v>
+        <v>12311</v>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
@@ -1227,11 +1227,11 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:09:22.890Z</t>
+          <t>2026-02-27T18:09:46.255Z</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>2972</v>
+        <v>3638</v>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
@@ -1258,11 +1258,11 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:09:25.863Z</t>
+          <t>2026-02-27T18:09:49.894Z</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>1710</v>
+        <v>1689</v>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
@@ -1289,11 +1289,11 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:09:27.573Z</t>
+          <t>2026-02-27T18:09:51.583Z</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>2346</v>
+        <v>3118</v>
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
@@ -1320,11 +1320,11 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:09:29.919Z</t>
+          <t>2026-02-27T18:09:54.701Z</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
@@ -1351,11 +1351,11 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:09:30.212Z</t>
+          <t>2026-02-27T18:09:54.994Z</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>9891</v>
+        <v>11911</v>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
@@ -1382,11 +1382,11 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:09:40.103Z</t>
+          <t>2026-02-27T18:10:06.907Z</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>2992</v>
+        <v>3653</v>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
@@ -1413,11 +1413,11 @@
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:09:43.095Z</t>
+          <t>2026-02-27T18:10:10.561Z</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>85</v>
+        <v>670</v>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
@@ -1444,11 +1444,11 @@
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:09:43.180Z</t>
+          <t>2026-02-27T18:10:11.232Z</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>13</v>
+        <v>2432</v>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
@@ -1475,11 +1475,11 @@
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:09:43.193Z</t>
+          <t>2026-02-27T18:10:13.664Z</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>3347</v>
+        <v>3375</v>
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
@@ -1506,11 +1506,11 @@
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:09:48.860Z</t>
+          <t>2026-02-27T18:10:19.856Z</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
@@ -1537,11 +1537,11 @@
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:09:49.415Z</t>
+          <t>2026-02-27T18:10:20.418Z</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:09:49.950Z</t>
+          <t>2026-02-27T18:10:20.960Z</t>
         </is>
       </c>
       <c r="E30" s="9" t="n">
@@ -1599,11 +1599,11 @@
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:09:50.484Z</t>
+          <t>2026-02-27T18:10:21.494Z</t>
         </is>
       </c>
       <c r="E31" s="9" t="n">
-        <v>1604</v>
+        <v>1625</v>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
@@ -1630,11 +1630,11 @@
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:09:52.088Z</t>
+          <t>2026-02-27T18:10:23.120Z</t>
         </is>
       </c>
       <c r="E32" s="9" t="n">
-        <v>863</v>
+        <v>846</v>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
@@ -1661,11 +1661,11 @@
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:09:52.952Z</t>
+          <t>2026-02-27T18:10:23.967Z</t>
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>816</v>
+        <v>831</v>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
@@ -1692,11 +1692,11 @@
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:09:53.768Z</t>
+          <t>2026-02-27T18:10:24.799Z</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
@@ -1723,11 +1723,11 @@
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:09:54.567Z</t>
+          <t>2026-02-27T18:10:25.599Z</t>
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>5372</v>
+        <v>6136</v>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
@@ -1754,11 +1754,11 @@
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:09:59.939Z</t>
+          <t>2026-02-27T18:10:31.735Z</t>
         </is>
       </c>
       <c r="E36" s="9" t="n">
-        <v>2656</v>
+        <v>3487</v>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
@@ -1785,11 +1785,11 @@
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:10:02.596Z</t>
+          <t>2026-02-27T18:10:35.223Z</t>
         </is>
       </c>
       <c r="E37" s="9" t="n">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
@@ -1816,11 +1816,11 @@
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:10:03.038Z</t>
+          <t>2026-02-27T18:10:35.671Z</t>
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
@@ -1847,11 +1847,11 @@
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:10:03.469Z</t>
+          <t>2026-02-27T18:10:36.098Z</t>
         </is>
       </c>
       <c r="E39" s="9" t="n">
-        <v>457</v>
+        <v>433</v>
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
@@ -1878,11 +1878,11 @@
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:10:03.927Z</t>
+          <t>2026-02-27T18:10:36.531Z</t>
         </is>
       </c>
       <c r="E40" s="9" t="n">
-        <v>765</v>
+        <v>782</v>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
@@ -1909,11 +1909,11 @@
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:10:04.695Z</t>
+          <t>2026-02-27T18:10:37.314Z</t>
         </is>
       </c>
       <c r="E41" s="9" t="n">
-        <v>4161</v>
+        <v>4802</v>
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
@@ -1940,11 +1940,11 @@
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:10:08.856Z</t>
+          <t>2026-02-27T18:10:42.116Z</t>
         </is>
       </c>
       <c r="E42" s="9" t="n">
-        <v>5216</v>
+        <v>5907</v>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
@@ -1971,11 +1971,11 @@
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:10:14.072Z</t>
+          <t>2026-02-27T18:10:48.023Z</t>
         </is>
       </c>
       <c r="E43" s="9" t="n">
-        <v>1998</v>
+        <v>1977</v>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
@@ -2002,11 +2002,11 @@
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:10:16.071Z</t>
+          <t>2026-02-27T18:10:50.000Z</t>
         </is>
       </c>
       <c r="E44" s="9" t="n">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
@@ -2033,11 +2033,11 @@
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:10:16.409Z</t>
+          <t>2026-02-27T18:10:50.330Z</t>
         </is>
       </c>
       <c r="E45" s="9" t="n">
-        <v>2367</v>
+        <v>2359</v>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
@@ -2064,11 +2064,11 @@
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:10:18.777Z</t>
+          <t>2026-02-27T18:10:52.689Z</t>
         </is>
       </c>
       <c r="E46" s="9" t="n">
-        <v>1369</v>
+        <v>1356</v>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
@@ -2095,11 +2095,11 @@
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:10:20.146Z</t>
+          <t>2026-02-27T18:10:54.045Z</t>
         </is>
       </c>
       <c r="E47" s="9" t="n">
-        <v>4501</v>
+        <v>4531</v>
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:10:24.647Z</t>
+          <t>2026-02-27T18:10:58.576Z</t>
         </is>
       </c>
       <c r="E48" s="9" t="n">
-        <v>1576</v>
+        <v>1580</v>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
@@ -2157,11 +2157,11 @@
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>2026-02-27T16:10:26.223Z</t>
+          <t>2026-02-27T18:11:00.156Z</t>
         </is>
       </c>
       <c r="E49" s="9" t="n">
-        <v>188</v>
+        <v>492</v>
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>

--- a/Testing/TEST_RESULTS.xlsx
+++ b/Testing/TEST_RESULTS.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-02T10:17:26.251Z</t>
+          <t>2026-03-02T11:24:09.324Z</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-02T10:17:29.171Z</t>
+          <t>2026-03-02T11:26:15.806Z</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.92 seconds</t>
+          <t>126.48 seconds</t>
         </is>
       </c>
     </row>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8">
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9">
@@ -618,17 +618,17 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -639,17 +639,17 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -660,17 +660,17 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -747,33 +747,1428 @@
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
+          <t>T01</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Login Admin (GUI)</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:24:10.802Z</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>3364</v>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>T02</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Open Admin Panel</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:24:14.166Z</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>695</v>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Create Admin user</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:24:14.861Z</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>1696</v>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>T04</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Login nuovo Admin</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:24:16.557Z</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>3280</v>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>T05</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Logout Admin-test</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:24:19.838Z</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>308</v>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Disable Admin-test</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:24:20.146Z</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>3339</v>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>T07</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Login utente disabilitato</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:24:23.486Z</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>2755</v>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>T08</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Riattivazione Admin-test</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:24:26.242Z</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>3269</v>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>T09</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Login post-riattivazione</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:24:29.511Z</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>2426</v>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Delete Admin-test</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:24:31.938Z</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>3556</v>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>T11</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Verify DB clean (API)</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:24:35.494Z</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>689</v>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Create Trader user</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:24:36.183Z</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>4118</v>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>T13</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Login Trader</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:24:40.301Z</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>3068</v>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>T14</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Logout Trader</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:24:43.370Z</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>289</v>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>T15</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Disable/Enable Trader cycle</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:24:43.660Z</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>11954</v>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>T16</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Delete Trader</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:24:55.615Z</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>3765</v>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>T17</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Create Viewer user</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:24:59.381Z</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>1687</v>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>T18</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Login Viewer</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:25:01.068Z</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>T19</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Logout Viewer</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:25:04.284Z</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>309</v>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Disable/Enable Viewer cycle</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:25:04.593Z</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>12214</v>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>T21</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Delete Viewer</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:25:16.807Z</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>4659</v>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>T22</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Verify DB clean (API)</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:25:21.466Z</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>791</v>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>T23</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Verify GUI clean</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:25:22.258Z</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>2993</v>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>T24</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Create users for Section 2</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:25:25.251Z</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>3413</v>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>T25</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>Drag &amp; Drop column</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:25:32.011Z</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>553</v>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>T26</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Hide column</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:25:32.565Z</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>534</v>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>T27</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>Show column</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:25:33.100Z</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>535</v>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>T28</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>Reset All Columns</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:25:33.636Z</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>1700</v>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>T29</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>Sort ascending</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:25:35.336Z</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>897</v>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>T30</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>Sort descending</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:25:36.233Z</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>879</v>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>T31</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>Sort different column</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:25:37.112Z</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>937</v>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>T32</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>Persist country tab after logout</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:25:38.050Z</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>6306</v>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>T33</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>Persist sort after logout</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:25:44.357Z</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>3737</v>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>T34</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>Single filter</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:25:48.094Z</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>454</v>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>T35</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>Multiple filters</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:25:48.548Z</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>435</v>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G38" s="9" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>T36</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>Remove one filter</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:25:48.984Z</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>434</v>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G39" s="9" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>T37</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>Clear all filters</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:25:49.418Z</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>815</v>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G40" s="9" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>T38</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>Mixed modifications</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:25:50.234Z</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>5711</v>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G41" s="9" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>T39</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>Persist all after reload</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:25:55.945Z</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="n">
+        <v>6188</v>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G42" s="9" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>T40</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>Complete reset</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:26:02.133Z</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>2040</v>
+      </c>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>T42</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>Login admin for RFQ tests</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:26:04.174Z</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="n">
+        <v>359</v>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G44" s="9" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>T43</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>Double-click bond row opens RFQ window</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:26:04.533Z</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>2366</v>
+      </c>
+      <c r="F45" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G45" s="9" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>T44</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>RFQ window displays pricing data</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:26:06.900Z</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="n">
+        <v>1364</v>
+      </c>
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G46" s="9" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>T45</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>RFQ window draggable and closable</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:26:08.264Z</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="n">
+        <v>4873</v>
+      </c>
+      <c r="F47" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G47" s="9" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>T46</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>Open RFQ from OPEN RFQ button</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:26:13.137Z</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="n">
+        <v>1670</v>
+      </c>
+      <c r="F48" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G48" s="9" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
           <t>T47</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B49" s="9" t="inlineStr">
         <is>
           <t>Final cleanup</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>GUI</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>2026-03-02T10:17:27.665Z</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>828</v>
-      </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="n"/>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>GUI</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>2026-03-02T11:26:14.807Z</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="n">
+        <v>556</v>
+      </c>
+      <c r="F49" s="10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G49" s="9" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Testing/TEST_RESULTS.xlsx
+++ b/Testing/TEST_RESULTS.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-02T11:24:09.324Z</t>
+          <t>2026-03-02T13:33:06.854Z</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-02T11:26:15.806Z</t>
+          <t>2026-03-02T13:35:36.737Z</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>126.48 seconds</t>
+          <t>149.88 seconds</t>
         </is>
       </c>
     </row>
@@ -762,11 +762,11 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:24:10.802Z</t>
+          <t>2026-03-02T13:33:15.243Z</t>
         </is>
       </c>
       <c r="E4" s="9" t="n">
-        <v>3364</v>
+        <v>6865</v>
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
@@ -793,11 +793,11 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:24:14.166Z</t>
+          <t>2026-03-02T13:33:22.109Z</t>
         </is>
       </c>
       <c r="E5" s="9" t="n">
-        <v>695</v>
+        <v>989</v>
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
@@ -824,11 +824,11 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:24:14.861Z</t>
+          <t>2026-03-02T13:33:23.098Z</t>
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>1696</v>
+        <v>1770</v>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:24:16.557Z</t>
+          <t>2026-03-02T13:33:24.869Z</t>
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>3280</v>
+        <v>4349</v>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
@@ -886,11 +886,11 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:24:19.838Z</t>
+          <t>2026-03-02T13:33:29.218Z</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>308</v>
+        <v>369</v>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
@@ -917,11 +917,11 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:24:20.146Z</t>
+          <t>2026-03-02T13:33:29.588Z</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>3339</v>
+        <v>4011</v>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
@@ -948,11 +948,11 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:24:23.486Z</t>
+          <t>2026-03-02T13:33:33.599Z</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>2755</v>
+        <v>2923</v>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
@@ -979,11 +979,11 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:24:26.242Z</t>
+          <t>2026-03-02T13:33:36.522Z</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>3269</v>
+        <v>4000</v>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
@@ -1010,11 +1010,11 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:24:29.511Z</t>
+          <t>2026-03-02T13:33:40.522Z</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>2426</v>
+        <v>2877</v>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
@@ -1041,11 +1041,11 @@
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:24:31.938Z</t>
+          <t>2026-03-02T13:33:43.399Z</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>3556</v>
+        <v>4682</v>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
@@ -1072,11 +1072,11 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:24:35.494Z</t>
+          <t>2026-03-02T13:33:48.081Z</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>689</v>
+        <v>726</v>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
@@ -1103,11 +1103,11 @@
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:24:36.183Z</t>
+          <t>2026-03-02T13:33:48.807Z</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>4118</v>
+        <v>5097</v>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
@@ -1134,11 +1134,11 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:24:40.301Z</t>
+          <t>2026-03-02T13:33:53.904Z</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>3068</v>
+        <v>3625</v>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
@@ -1165,11 +1165,11 @@
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:24:43.370Z</t>
+          <t>2026-03-02T13:33:57.529Z</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>289</v>
+        <v>335</v>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
@@ -1196,11 +1196,11 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:24:43.660Z</t>
+          <t>2026-03-02T13:33:57.864Z</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>11954</v>
+        <v>13918</v>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
@@ -1227,11 +1227,11 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:24:55.615Z</t>
+          <t>2026-03-02T13:34:11.783Z</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>3765</v>
+        <v>4738</v>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
@@ -1258,11 +1258,11 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:24:59.381Z</t>
+          <t>2026-03-02T13:34:16.522Z</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>1687</v>
+        <v>1715</v>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
@@ -1289,11 +1289,11 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:25:01.068Z</t>
+          <t>2026-03-02T13:34:18.237Z</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>3215</v>
+        <v>3861</v>
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
@@ -1320,11 +1320,11 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:25:04.284Z</t>
+          <t>2026-03-02T13:34:22.099Z</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>309</v>
+        <v>365</v>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
@@ -1351,11 +1351,11 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:25:04.593Z</t>
+          <t>2026-03-02T13:34:22.464Z</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>12214</v>
+        <v>13949</v>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
@@ -1382,11 +1382,11 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:25:16.807Z</t>
+          <t>2026-03-02T13:34:36.413Z</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>4659</v>
+        <v>4388</v>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
@@ -1413,11 +1413,11 @@
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:25:21.466Z</t>
+          <t>2026-03-02T13:34:40.801Z</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>791</v>
+        <v>811</v>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
@@ -1444,11 +1444,11 @@
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:25:22.258Z</t>
+          <t>2026-03-02T13:34:41.613Z</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>2993</v>
+        <v>3196</v>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
@@ -1475,11 +1475,11 @@
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:25:25.251Z</t>
+          <t>2026-03-02T13:34:44.810Z</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>3413</v>
+        <v>3612</v>
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
@@ -1506,11 +1506,11 @@
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:25:32.011Z</t>
+          <t>2026-03-02T13:34:51.892Z</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>553</v>
+        <v>590</v>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
@@ -1537,11 +1537,11 @@
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:25:32.565Z</t>
+          <t>2026-03-02T13:34:52.483Z</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>534</v>
+        <v>558</v>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
@@ -1568,11 +1568,11 @@
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:25:33.100Z</t>
+          <t>2026-03-02T13:34:53.041Z</t>
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>535</v>
+        <v>554</v>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
@@ -1599,11 +1599,11 @@
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:25:33.636Z</t>
+          <t>2026-03-02T13:34:53.595Z</t>
         </is>
       </c>
       <c r="E31" s="9" t="n">
-        <v>1700</v>
+        <v>1741</v>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
@@ -1630,11 +1630,11 @@
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:25:35.336Z</t>
+          <t>2026-03-02T13:34:55.337Z</t>
         </is>
       </c>
       <c r="E32" s="9" t="n">
-        <v>897</v>
+        <v>1010</v>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
@@ -1661,11 +1661,11 @@
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:25:36.233Z</t>
+          <t>2026-03-02T13:34:56.348Z</t>
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>879</v>
+        <v>944</v>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
@@ -1692,11 +1692,11 @@
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:25:37.112Z</t>
+          <t>2026-03-02T13:34:57.292Z</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>937</v>
+        <v>1062</v>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
@@ -1723,11 +1723,11 @@
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:25:38.050Z</t>
+          <t>2026-03-02T13:34:58.354Z</t>
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>6306</v>
+        <v>6251</v>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
@@ -1754,11 +1754,11 @@
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:25:44.357Z</t>
+          <t>2026-03-02T13:35:04.605Z</t>
         </is>
       </c>
       <c r="E36" s="9" t="n">
-        <v>3737</v>
+        <v>3877</v>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
@@ -1785,11 +1785,11 @@
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:25:48.094Z</t>
+          <t>2026-03-02T13:35:08.483Z</t>
         </is>
       </c>
       <c r="E37" s="9" t="n">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
@@ -1816,11 +1816,11 @@
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:25:48.548Z</t>
+          <t>2026-03-02T13:35:08.944Z</t>
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
@@ -1847,11 +1847,11 @@
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:25:48.984Z</t>
+          <t>2026-03-02T13:35:09.387Z</t>
         </is>
       </c>
       <c r="E39" s="9" t="n">
-        <v>434</v>
+        <v>450</v>
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
@@ -1878,11 +1878,11 @@
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:25:49.418Z</t>
+          <t>2026-03-02T13:35:09.838Z</t>
         </is>
       </c>
       <c r="E40" s="9" t="n">
-        <v>815</v>
+        <v>1009</v>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
@@ -1909,11 +1909,11 @@
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:25:50.234Z</t>
+          <t>2026-03-02T13:35:10.849Z</t>
         </is>
       </c>
       <c r="E41" s="9" t="n">
-        <v>5711</v>
+        <v>5613</v>
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
@@ -1940,11 +1940,11 @@
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:25:55.945Z</t>
+          <t>2026-03-02T13:35:16.462Z</t>
         </is>
       </c>
       <c r="E42" s="9" t="n">
-        <v>6188</v>
+        <v>6292</v>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
@@ -1971,11 +1971,11 @@
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:26:02.133Z</t>
+          <t>2026-03-02T13:35:22.755Z</t>
         </is>
       </c>
       <c r="E43" s="9" t="n">
-        <v>2040</v>
+        <v>2078</v>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
@@ -2002,11 +2002,11 @@
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:26:04.174Z</t>
+          <t>2026-03-02T13:35:24.834Z</t>
         </is>
       </c>
       <c r="E44" s="9" t="n">
-        <v>359</v>
+        <v>335</v>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
@@ -2033,11 +2033,11 @@
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:26:04.533Z</t>
+          <t>2026-03-02T13:35:25.169Z</t>
         </is>
       </c>
       <c r="E45" s="9" t="n">
-        <v>2366</v>
+        <v>2384</v>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
@@ -2064,11 +2064,11 @@
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:26:06.900Z</t>
+          <t>2026-03-02T13:35:27.553Z</t>
         </is>
       </c>
       <c r="E46" s="9" t="n">
-        <v>1364</v>
+        <v>1368</v>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
@@ -2095,11 +2095,11 @@
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:26:08.264Z</t>
+          <t>2026-03-02T13:35:28.922Z</t>
         </is>
       </c>
       <c r="E47" s="9" t="n">
-        <v>4873</v>
+        <v>4706</v>
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:26:13.137Z</t>
+          <t>2026-03-02T13:35:33.628Z</t>
         </is>
       </c>
       <c r="E48" s="9" t="n">
-        <v>1670</v>
+        <v>1718</v>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
@@ -2157,11 +2157,11 @@
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T11:26:14.807Z</t>
+          <t>2026-03-02T13:35:35.346Z</t>
         </is>
       </c>
       <c r="E49" s="9" t="n">
-        <v>556</v>
+        <v>625</v>
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>

--- a/Testing/TEST_RESULTS.xlsx
+++ b/Testing/TEST_RESULTS.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-02T13:33:06.854Z</t>
+          <t>2026-03-02T15:10:55.212Z</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-02T13:35:36.737Z</t>
+          <t>2026-03-02T15:13:15.693Z</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>149.88 seconds</t>
+          <t>140.48 seconds</t>
         </is>
       </c>
     </row>
@@ -762,11 +762,11 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:33:15.243Z</t>
+          <t>2026-03-02T15:10:58.571Z</t>
         </is>
       </c>
       <c r="E4" s="9" t="n">
-        <v>6865</v>
+        <v>7284</v>
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
@@ -793,11 +793,11 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:33:22.109Z</t>
+          <t>2026-03-02T15:11:05.856Z</t>
         </is>
       </c>
       <c r="E5" s="9" t="n">
-        <v>989</v>
+        <v>1190</v>
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
@@ -824,11 +824,11 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:33:23.098Z</t>
+          <t>2026-03-02T15:11:07.046Z</t>
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>1770</v>
+        <v>1928</v>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:33:24.869Z</t>
+          <t>2026-03-02T15:11:08.975Z</t>
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>4349</v>
+        <v>4715</v>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
@@ -886,11 +886,11 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:33:29.218Z</t>
+          <t>2026-03-02T15:11:13.691Z</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>369</v>
+        <v>386</v>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
@@ -917,11 +917,11 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:33:29.588Z</t>
+          <t>2026-03-02T15:11:14.078Z</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>4011</v>
+        <v>4210</v>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
@@ -948,11 +948,11 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:33:33.599Z</t>
+          <t>2026-03-02T15:11:18.288Z</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>2923</v>
+        <v>2802</v>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
@@ -979,11 +979,11 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:33:36.522Z</t>
+          <t>2026-03-02T15:11:21.090Z</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>4000</v>
+        <v>3727</v>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
@@ -1010,11 +1010,11 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:33:40.522Z</t>
+          <t>2026-03-02T15:11:24.817Z</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>2877</v>
+        <v>2708</v>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
@@ -1041,11 +1041,11 @@
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:33:43.399Z</t>
+          <t>2026-03-02T15:11:27.525Z</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>4682</v>
+        <v>4256</v>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
@@ -1072,11 +1072,11 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:33:48.081Z</t>
+          <t>2026-03-02T15:11:31.781Z</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>726</v>
+        <v>823</v>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
@@ -1103,11 +1103,11 @@
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:33:48.807Z</t>
+          <t>2026-03-02T15:11:32.605Z</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>5097</v>
+        <v>4864</v>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
@@ -1134,11 +1134,11 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:33:53.904Z</t>
+          <t>2026-03-02T15:11:37.469Z</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>3625</v>
+        <v>3703</v>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
@@ -1165,11 +1165,11 @@
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:33:57.529Z</t>
+          <t>2026-03-02T15:11:41.172Z</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
@@ -1196,11 +1196,11 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:33:57.864Z</t>
+          <t>2026-03-02T15:11:41.521Z</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>13918</v>
+        <v>12947</v>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
@@ -1227,11 +1227,11 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:34:11.783Z</t>
+          <t>2026-03-02T15:11:54.469Z</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>4738</v>
+        <v>4157</v>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
@@ -1258,11 +1258,11 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:34:16.522Z</t>
+          <t>2026-03-02T15:11:58.627Z</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>1715</v>
+        <v>1722</v>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
@@ -1289,11 +1289,11 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:34:18.237Z</t>
+          <t>2026-03-02T15:12:00.349Z</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>3861</v>
+        <v>3453</v>
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
@@ -1320,11 +1320,11 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:34:22.099Z</t>
+          <t>2026-03-02T15:12:03.803Z</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>365</v>
+        <v>305</v>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
@@ -1351,11 +1351,11 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:34:22.464Z</t>
+          <t>2026-03-02T15:12:04.108Z</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>13949</v>
+        <v>13260</v>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
@@ -1382,11 +1382,11 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:34:36.413Z</t>
+          <t>2026-03-02T15:12:17.369Z</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>4388</v>
+        <v>4389</v>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
@@ -1413,11 +1413,11 @@
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:34:40.801Z</t>
+          <t>2026-03-02T15:12:21.759Z</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>811</v>
+        <v>739</v>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
@@ -1444,11 +1444,11 @@
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:34:41.613Z</t>
+          <t>2026-03-02T15:12:22.498Z</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>3196</v>
+        <v>2832</v>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
@@ -1475,11 +1475,11 @@
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:34:44.810Z</t>
+          <t>2026-03-02T15:12:25.331Z</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>3612</v>
+        <v>3433</v>
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
@@ -1506,11 +1506,11 @@
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:34:51.892Z</t>
+          <t>2026-03-02T15:12:32.102Z</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>590</v>
+        <v>577</v>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
@@ -1537,11 +1537,11 @@
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:34:52.483Z</t>
+          <t>2026-03-02T15:12:32.680Z</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>558</v>
+        <v>535</v>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
@@ -1568,11 +1568,11 @@
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:34:53.041Z</t>
+          <t>2026-03-02T15:12:33.216Z</t>
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>554</v>
+        <v>533</v>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
@@ -1599,11 +1599,11 @@
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:34:53.595Z</t>
+          <t>2026-03-02T15:12:33.749Z</t>
         </is>
       </c>
       <c r="E31" s="9" t="n">
-        <v>1741</v>
+        <v>1672</v>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
@@ -1630,11 +1630,11 @@
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:34:55.337Z</t>
+          <t>2026-03-02T15:12:35.422Z</t>
         </is>
       </c>
       <c r="E32" s="9" t="n">
-        <v>1010</v>
+        <v>890</v>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
@@ -1661,11 +1661,11 @@
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:34:56.348Z</t>
+          <t>2026-03-02T15:12:36.312Z</t>
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>944</v>
+        <v>933</v>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
@@ -1692,11 +1692,11 @@
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:34:57.292Z</t>
+          <t>2026-03-02T15:12:37.245Z</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>1062</v>
+        <v>837</v>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
@@ -1723,11 +1723,11 @@
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:34:58.354Z</t>
+          <t>2026-03-02T15:12:38.083Z</t>
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>6251</v>
+        <v>6363</v>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
@@ -1754,11 +1754,11 @@
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:35:04.605Z</t>
+          <t>2026-03-02T15:12:44.446Z</t>
         </is>
       </c>
       <c r="E36" s="9" t="n">
-        <v>3877</v>
+        <v>3802</v>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
@@ -1785,11 +1785,11 @@
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:35:08.483Z</t>
+          <t>2026-03-02T15:12:48.249Z</t>
         </is>
       </c>
       <c r="E37" s="9" t="n">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
@@ -1816,11 +1816,11 @@
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:35:08.944Z</t>
+          <t>2026-03-02T15:12:48.717Z</t>
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
@@ -1847,11 +1847,11 @@
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:35:09.387Z</t>
+          <t>2026-03-02T15:12:49.172Z</t>
         </is>
       </c>
       <c r="E39" s="9" t="n">
-        <v>450</v>
+        <v>467</v>
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
@@ -1878,11 +1878,11 @@
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:35:09.838Z</t>
+          <t>2026-03-02T15:12:49.639Z</t>
         </is>
       </c>
       <c r="E40" s="9" t="n">
-        <v>1009</v>
+        <v>825</v>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
@@ -1909,11 +1909,11 @@
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:35:10.849Z</t>
+          <t>2026-03-02T15:12:50.465Z</t>
         </is>
       </c>
       <c r="E41" s="9" t="n">
-        <v>5613</v>
+        <v>5271</v>
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
@@ -1940,11 +1940,11 @@
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:35:16.462Z</t>
+          <t>2026-03-02T15:12:55.737Z</t>
         </is>
       </c>
       <c r="E42" s="9" t="n">
-        <v>6292</v>
+        <v>6076</v>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
@@ -1971,11 +1971,11 @@
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:35:22.755Z</t>
+          <t>2026-03-02T15:13:01.814Z</t>
         </is>
       </c>
       <c r="E43" s="9" t="n">
-        <v>2078</v>
+        <v>2100</v>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
@@ -2002,11 +2002,11 @@
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:35:24.834Z</t>
+          <t>2026-03-02T15:13:03.915Z</t>
         </is>
       </c>
       <c r="E44" s="9" t="n">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
@@ -2033,11 +2033,11 @@
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:35:25.169Z</t>
+          <t>2026-03-02T15:13:04.244Z</t>
         </is>
       </c>
       <c r="E45" s="9" t="n">
-        <v>2384</v>
+        <v>2370</v>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
@@ -2064,11 +2064,11 @@
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:35:27.553Z</t>
+          <t>2026-03-02T15:13:06.615Z</t>
         </is>
       </c>
       <c r="E46" s="9" t="n">
-        <v>1368</v>
+        <v>1350</v>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
@@ -2095,11 +2095,11 @@
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:35:28.922Z</t>
+          <t>2026-03-02T15:13:07.965Z</t>
         </is>
       </c>
       <c r="E47" s="9" t="n">
-        <v>4706</v>
+        <v>4559</v>
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:35:33.628Z</t>
+          <t>2026-03-02T15:13:12.525Z</t>
         </is>
       </c>
       <c r="E48" s="9" t="n">
-        <v>1718</v>
+        <v>1579</v>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
@@ -2157,11 +2157,11 @@
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T13:35:35.346Z</t>
+          <t>2026-03-02T15:13:14.104Z</t>
         </is>
       </c>
       <c r="E49" s="9" t="n">
-        <v>625</v>
+        <v>744</v>
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>

--- a/Testing/TEST_RESULTS.xlsx
+++ b/Testing/TEST_RESULTS.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-02T15:10:55.212Z</t>
+          <t>2026-03-03T15:47:54.944Z</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-02T15:13:15.693Z</t>
+          <t>2026-03-03T15:51:18.023Z</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>140.48 seconds</t>
+          <t>203.08 seconds</t>
         </is>
       </c>
     </row>
@@ -762,11 +762,11 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:10:58.571Z</t>
+          <t>2026-03-03T15:47:57.696Z</t>
         </is>
       </c>
       <c r="E4" s="9" t="n">
-        <v>7284</v>
+        <v>5382</v>
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
@@ -793,11 +793,11 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:11:05.856Z</t>
+          <t>2026-03-03T15:48:03.078Z</t>
         </is>
       </c>
       <c r="E5" s="9" t="n">
-        <v>1190</v>
+        <v>734</v>
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
@@ -824,11 +824,11 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:11:07.046Z</t>
+          <t>2026-03-03T15:48:03.812Z</t>
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>1928</v>
+        <v>1736</v>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:11:08.975Z</t>
+          <t>2026-03-03T15:48:05.548Z</t>
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>4715</v>
+        <v>3903</v>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
@@ -886,11 +886,11 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:11:13.691Z</t>
+          <t>2026-03-03T15:48:09.451Z</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>386</v>
+        <v>321</v>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
@@ -917,11 +917,11 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:11:14.078Z</t>
+          <t>2026-03-03T15:48:09.772Z</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>4210</v>
+        <v>3696</v>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
@@ -948,11 +948,11 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:11:18.288Z</t>
+          <t>2026-03-03T15:48:13.469Z</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>2802</v>
+        <v>2772</v>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
@@ -979,11 +979,11 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:11:21.090Z</t>
+          <t>2026-03-03T15:48:16.240Z</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>3727</v>
+        <v>4230</v>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
@@ -1010,11 +1010,11 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:11:24.817Z</t>
+          <t>2026-03-03T15:48:20.470Z</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>2708</v>
+        <v>2648</v>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
@@ -1041,11 +1041,11 @@
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:11:27.525Z</t>
+          <t>2026-03-03T15:48:23.118Z</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>4256</v>
+        <v>4113</v>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
@@ -1072,11 +1072,11 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:11:31.781Z</t>
+          <t>2026-03-03T15:48:27.232Z</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>823</v>
+        <v>16168</v>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
@@ -1103,11 +1103,11 @@
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:11:32.605Z</t>
+          <t>2026-03-03T15:48:43.400Z</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>4864</v>
+        <v>15137</v>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
@@ -1134,11 +1134,11 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:11:37.469Z</t>
+          <t>2026-03-03T15:48:58.537Z</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>3703</v>
+        <v>3793</v>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
@@ -1165,11 +1165,11 @@
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:11:41.172Z</t>
+          <t>2026-03-03T15:49:02.331Z</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>349</v>
+        <v>333</v>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
@@ -1196,11 +1196,11 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:11:41.521Z</t>
+          <t>2026-03-03T15:49:02.665Z</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>12947</v>
+        <v>12711</v>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
@@ -1227,11 +1227,11 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:11:54.469Z</t>
+          <t>2026-03-03T15:49:15.377Z</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>4157</v>
+        <v>4206</v>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
@@ -1258,11 +1258,11 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:11:58.627Z</t>
+          <t>2026-03-03T15:49:19.583Z</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>1722</v>
+        <v>1718</v>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
@@ -1289,11 +1289,11 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:12:00.349Z</t>
+          <t>2026-03-03T15:49:21.301Z</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>3453</v>
+        <v>3473</v>
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
@@ -1320,11 +1320,11 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:12:03.803Z</t>
+          <t>2026-03-03T15:49:24.774Z</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
@@ -1351,11 +1351,11 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:12:04.108Z</t>
+          <t>2026-03-03T15:49:25.080Z</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>13260</v>
+        <v>12875</v>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
@@ -1382,11 +1382,11 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:12:17.369Z</t>
+          <t>2026-03-03T15:49:37.956Z</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>4389</v>
+        <v>4012</v>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
@@ -1413,11 +1413,11 @@
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:12:21.759Z</t>
+          <t>2026-03-03T15:49:41.968Z</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>739</v>
+        <v>16038</v>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
@@ -1444,11 +1444,11 @@
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:12:22.498Z</t>
+          <t>2026-03-03T15:49:58.006Z</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>2832</v>
+        <v>13713</v>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
@@ -1475,11 +1475,11 @@
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:12:25.331Z</t>
+          <t>2026-03-03T15:50:11.719Z</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>3433</v>
+        <v>3386</v>
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
@@ -1506,11 +1506,11 @@
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:12:32.102Z</t>
+          <t>2026-03-03T15:50:34.292Z</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
@@ -1537,11 +1537,11 @@
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:12:32.680Z</t>
+          <t>2026-03-03T15:50:34.862Z</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
@@ -1568,11 +1568,11 @@
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:12:33.216Z</t>
+          <t>2026-03-03T15:50:35.393Z</t>
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
@@ -1599,11 +1599,11 @@
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:12:33.749Z</t>
+          <t>2026-03-03T15:50:35.934Z</t>
         </is>
       </c>
       <c r="E31" s="9" t="n">
-        <v>1672</v>
+        <v>1682</v>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
@@ -1630,11 +1630,11 @@
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:12:35.422Z</t>
+          <t>2026-03-03T15:50:37.617Z</t>
         </is>
       </c>
       <c r="E32" s="9" t="n">
-        <v>890</v>
+        <v>898</v>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
@@ -1661,11 +1661,11 @@
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:12:36.312Z</t>
+          <t>2026-03-03T15:50:38.516Z</t>
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>933</v>
+        <v>866</v>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
@@ -1692,11 +1692,11 @@
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:12:37.245Z</t>
+          <t>2026-03-03T15:50:39.383Z</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
@@ -1723,11 +1723,11 @@
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:12:38.083Z</t>
+          <t>2026-03-03T15:50:40.212Z</t>
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>6363</v>
+        <v>6476</v>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
@@ -1754,11 +1754,11 @@
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:12:44.446Z</t>
+          <t>2026-03-03T15:50:46.689Z</t>
         </is>
       </c>
       <c r="E36" s="9" t="n">
-        <v>3802</v>
+        <v>3865</v>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
@@ -1785,11 +1785,11 @@
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:12:48.249Z</t>
+          <t>2026-03-03T15:50:50.555Z</t>
         </is>
       </c>
       <c r="E37" s="9" t="n">
-        <v>468</v>
+        <v>450</v>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
@@ -1816,11 +1816,11 @@
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:12:48.717Z</t>
+          <t>2026-03-03T15:50:51.006Z</t>
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>454</v>
+        <v>426</v>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
@@ -1847,11 +1847,11 @@
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:12:49.172Z</t>
+          <t>2026-03-03T15:50:51.432Z</t>
         </is>
       </c>
       <c r="E39" s="9" t="n">
-        <v>467</v>
+        <v>446</v>
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
@@ -1878,11 +1878,11 @@
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:12:49.639Z</t>
+          <t>2026-03-03T15:50:51.878Z</t>
         </is>
       </c>
       <c r="E40" s="9" t="n">
-        <v>825</v>
+        <v>839</v>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
@@ -1909,11 +1909,11 @@
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:12:50.465Z</t>
+          <t>2026-03-03T15:50:52.719Z</t>
         </is>
       </c>
       <c r="E41" s="9" t="n">
-        <v>5271</v>
+        <v>5272</v>
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
@@ -1940,11 +1940,11 @@
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:12:55.737Z</t>
+          <t>2026-03-03T15:50:57.991Z</t>
         </is>
       </c>
       <c r="E42" s="9" t="n">
-        <v>6076</v>
+        <v>6177</v>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
@@ -1971,11 +1971,11 @@
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:13:01.814Z</t>
+          <t>2026-03-03T15:51:04.168Z</t>
         </is>
       </c>
       <c r="E43" s="9" t="n">
-        <v>2100</v>
+        <v>2038</v>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
@@ -2002,11 +2002,11 @@
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:13:03.915Z</t>
+          <t>2026-03-03T15:51:06.207Z</t>
         </is>
       </c>
       <c r="E44" s="9" t="n">
-        <v>328</v>
+        <v>379</v>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
@@ -2033,11 +2033,11 @@
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:13:04.244Z</t>
+          <t>2026-03-03T15:51:06.587Z</t>
         </is>
       </c>
       <c r="E45" s="9" t="n">
-        <v>2370</v>
+        <v>2379</v>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
@@ -2064,11 +2064,11 @@
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:13:06.615Z</t>
+          <t>2026-03-03T15:51:08.966Z</t>
         </is>
       </c>
       <c r="E46" s="9" t="n">
-        <v>1350</v>
+        <v>1363</v>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
@@ -2095,11 +2095,11 @@
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:13:07.965Z</t>
+          <t>2026-03-03T15:51:10.329Z</t>
         </is>
       </c>
       <c r="E47" s="9" t="n">
-        <v>4559</v>
+        <v>4616</v>
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:13:12.525Z</t>
+          <t>2026-03-03T15:51:14.945Z</t>
         </is>
       </c>
       <c r="E48" s="9" t="n">
-        <v>1579</v>
+        <v>1644</v>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
@@ -2157,11 +2157,11 @@
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>2026-03-02T15:13:14.104Z</t>
+          <t>2026-03-03T15:51:16.589Z</t>
         </is>
       </c>
       <c r="E49" s="9" t="n">
-        <v>744</v>
+        <v>605</v>
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>

--- a/Testing/TEST_RESULTS.xlsx
+++ b/Testing/TEST_RESULTS.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-03T15:47:54.944Z</t>
+          <t>2026-03-04T14:53:15.812Z</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-03T15:51:18.023Z</t>
+          <t>2026-03-04T14:55:31.804Z</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>203.08 seconds</t>
+          <t>135.99 seconds</t>
         </is>
       </c>
     </row>
@@ -762,11 +762,11 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:47:57.696Z</t>
+          <t>2026-03-04T14:53:22.897Z</t>
         </is>
       </c>
       <c r="E4" s="9" t="n">
-        <v>5382</v>
+        <v>2339</v>
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
@@ -793,11 +793,11 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:48:03.078Z</t>
+          <t>2026-03-04T14:53:25.236Z</t>
         </is>
       </c>
       <c r="E5" s="9" t="n">
-        <v>734</v>
+        <v>688</v>
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
@@ -824,11 +824,11 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:48:03.812Z</t>
+          <t>2026-03-04T14:53:25.924Z</t>
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>1736</v>
+        <v>1747</v>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
@@ -855,11 +855,11 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:48:05.548Z</t>
+          <t>2026-03-04T14:53:27.671Z</t>
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>3903</v>
+        <v>3152</v>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
@@ -886,11 +886,11 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:48:09.451Z</t>
+          <t>2026-03-04T14:53:30.823Z</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>321</v>
+        <v>393</v>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
@@ -917,11 +917,11 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:48:09.772Z</t>
+          <t>2026-03-04T14:53:31.217Z</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>3696</v>
+        <v>3794</v>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
@@ -948,11 +948,11 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:48:13.469Z</t>
+          <t>2026-03-04T14:53:35.012Z</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>2772</v>
+        <v>2818</v>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
@@ -979,11 +979,11 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:48:16.240Z</t>
+          <t>2026-03-04T14:53:37.830Z</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>4230</v>
+        <v>3802</v>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
@@ -1010,11 +1010,11 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:48:20.470Z</t>
+          <t>2026-03-04T14:53:41.633Z</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>2648</v>
+        <v>2871</v>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
@@ -1041,11 +1041,11 @@
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:48:23.118Z</t>
+          <t>2026-03-04T14:53:44.505Z</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>4113</v>
+        <v>4249</v>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
@@ -1072,11 +1072,11 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:48:27.232Z</t>
+          <t>2026-03-04T14:53:48.754Z</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>16168</v>
+        <v>701</v>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
@@ -1103,11 +1103,11 @@
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:48:43.400Z</t>
+          <t>2026-03-04T14:53:49.456Z</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>15137</v>
+        <v>4597</v>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
@@ -1134,11 +1134,11 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:48:58.537Z</t>
+          <t>2026-03-04T14:53:54.054Z</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>3793</v>
+        <v>3487</v>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
@@ -1165,11 +1165,11 @@
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:49:02.331Z</t>
+          <t>2026-03-04T14:53:57.541Z</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
@@ -1196,11 +1196,11 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:49:02.665Z</t>
+          <t>2026-03-04T14:53:57.866Z</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>12711</v>
+        <v>13032</v>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
@@ -1227,11 +1227,11 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:49:15.377Z</t>
+          <t>2026-03-04T14:54:10.899Z</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>4206</v>
+        <v>4220</v>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
@@ -1258,11 +1258,11 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:49:19.583Z</t>
+          <t>2026-03-04T14:54:15.120Z</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>1718</v>
+        <v>1744</v>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
@@ -1289,11 +1289,11 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:49:21.301Z</t>
+          <t>2026-03-04T14:54:16.865Z</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>3473</v>
+        <v>3458</v>
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
@@ -1320,11 +1320,11 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:49:24.774Z</t>
+          <t>2026-03-04T14:54:20.324Z</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>306</v>
+        <v>358</v>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
@@ -1351,11 +1351,11 @@
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:49:25.080Z</t>
+          <t>2026-03-04T14:54:20.683Z</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>12875</v>
+        <v>12870</v>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
@@ -1382,11 +1382,11 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:49:37.956Z</t>
+          <t>2026-03-04T14:54:33.553Z</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>4012</v>
+        <v>4198</v>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
@@ -1413,11 +1413,11 @@
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:49:41.968Z</t>
+          <t>2026-03-04T14:54:37.751Z</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>16038</v>
+        <v>706</v>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
@@ -1444,11 +1444,11 @@
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:49:58.006Z</t>
+          <t>2026-03-04T14:54:38.458Z</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>13713</v>
+        <v>2932</v>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
@@ -1475,11 +1475,11 @@
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:50:11.719Z</t>
+          <t>2026-03-04T14:54:41.390Z</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>3386</v>
+        <v>3413</v>
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
@@ -1506,11 +1506,11 @@
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:50:34.292Z</t>
+          <t>2026-03-04T14:54:48.057Z</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>570</v>
+        <v>585</v>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
@@ -1537,11 +1537,11 @@
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:50:34.862Z</t>
+          <t>2026-03-04T14:54:48.642Z</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
@@ -1568,11 +1568,11 @@
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:50:35.393Z</t>
+          <t>2026-03-04T14:54:49.178Z</t>
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
@@ -1599,11 +1599,11 @@
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:50:35.934Z</t>
+          <t>2026-03-04T14:54:49.723Z</t>
         </is>
       </c>
       <c r="E31" s="9" t="n">
-        <v>1682</v>
+        <v>1707</v>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
@@ -1630,11 +1630,11 @@
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:50:37.617Z</t>
+          <t>2026-03-04T14:54:51.430Z</t>
         </is>
       </c>
       <c r="E32" s="9" t="n">
-        <v>898</v>
+        <v>984</v>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
@@ -1661,11 +1661,11 @@
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:50:38.516Z</t>
+          <t>2026-03-04T14:54:52.414Z</t>
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>866</v>
+        <v>1004</v>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
@@ -1692,11 +1692,11 @@
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:50:39.383Z</t>
+          <t>2026-03-04T14:54:53.418Z</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>829</v>
+        <v>901</v>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
@@ -1723,11 +1723,11 @@
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:50:40.212Z</t>
+          <t>2026-03-04T14:54:54.320Z</t>
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>6476</v>
+        <v>6379</v>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
@@ -1754,11 +1754,11 @@
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:50:46.689Z</t>
+          <t>2026-03-04T14:55:00.700Z</t>
         </is>
       </c>
       <c r="E36" s="9" t="n">
-        <v>3865</v>
+        <v>3918</v>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
@@ -1785,11 +1785,11 @@
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:50:50.555Z</t>
+          <t>2026-03-04T14:55:04.619Z</t>
         </is>
       </c>
       <c r="E37" s="9" t="n">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
@@ -1816,11 +1816,11 @@
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:50:51.006Z</t>
+          <t>2026-03-04T14:55:05.083Z</t>
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>426</v>
+        <v>450</v>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:50:51.432Z</t>
+          <t>2026-03-04T14:55:05.533Z</t>
         </is>
       </c>
       <c r="E39" s="9" t="n">
@@ -1878,11 +1878,11 @@
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:50:51.878Z</t>
+          <t>2026-03-04T14:55:05.979Z</t>
         </is>
       </c>
       <c r="E40" s="9" t="n">
-        <v>839</v>
+        <v>894</v>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
@@ -1909,11 +1909,11 @@
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:50:52.719Z</t>
+          <t>2026-03-04T14:55:06.875Z</t>
         </is>
       </c>
       <c r="E41" s="9" t="n">
-        <v>5272</v>
+        <v>5441</v>
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
@@ -1940,11 +1940,11 @@
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:50:57.991Z</t>
+          <t>2026-03-04T14:55:12.317Z</t>
         </is>
       </c>
       <c r="E42" s="9" t="n">
-        <v>6177</v>
+        <v>6127</v>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
@@ -1971,11 +1971,11 @@
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:51:04.168Z</t>
+          <t>2026-03-04T14:55:18.445Z</t>
         </is>
       </c>
       <c r="E43" s="9" t="n">
-        <v>2038</v>
+        <v>2066</v>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
@@ -2002,11 +2002,11 @@
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:51:06.207Z</t>
+          <t>2026-03-04T14:55:20.511Z</t>
         </is>
       </c>
       <c r="E44" s="9" t="n">
-        <v>379</v>
+        <v>355</v>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
@@ -2033,11 +2033,11 @@
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:51:06.587Z</t>
+          <t>2026-03-04T14:55:20.866Z</t>
         </is>
       </c>
       <c r="E45" s="9" t="n">
-        <v>2379</v>
+        <v>2383</v>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
@@ -2064,11 +2064,11 @@
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:51:08.966Z</t>
+          <t>2026-03-04T14:55:23.249Z</t>
         </is>
       </c>
       <c r="E46" s="9" t="n">
-        <v>1363</v>
+        <v>1371</v>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
@@ -2095,11 +2095,11 @@
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:51:10.329Z</t>
+          <t>2026-03-04T14:55:24.620Z</t>
         </is>
       </c>
       <c r="E47" s="9" t="n">
-        <v>4616</v>
+        <v>4736</v>
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:51:14.945Z</t>
+          <t>2026-03-04T14:55:29.356Z</t>
         </is>
       </c>
       <c r="E48" s="9" t="n">
-        <v>1644</v>
+        <v>1608</v>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
@@ -2157,11 +2157,11 @@
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>2026-03-03T15:51:16.589Z</t>
+          <t>2026-03-04T14:55:30.965Z</t>
         </is>
       </c>
       <c r="E49" s="9" t="n">
-        <v>605</v>
+        <v>502</v>
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>
